--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="228">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -497,6 +497,9 @@
   </si>
   <si>
     <t>['12', '90']</t>
+  </si>
+  <si>
+    <t>['50', '90+6']</t>
   </si>
   <si>
     <t>['13', '73']</t>
@@ -1056,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP120"/>
+  <dimension ref="A1:BP121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1312,7 +1315,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1518,7 +1521,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -2136,7 +2139,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2217,7 +2220,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2548,7 +2551,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2960,7 +2963,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3041,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3166,7 +3169,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3372,7 +3375,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3990,7 +3993,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q15">
         <v>1.44</v>
@@ -4068,7 +4071,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ15">
         <v>0.63</v>
@@ -4196,7 +4199,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4402,7 +4405,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4814,7 +4817,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5020,7 +5023,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5226,7 +5229,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5432,7 +5435,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5844,7 +5847,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6050,7 +6053,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6334,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ26">
         <v>1.63</v>
@@ -6668,7 +6671,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6749,7 +6752,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR28">
         <v>1</v>
@@ -7080,7 +7083,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7492,7 +7495,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7904,7 +7907,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8110,7 +8113,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8522,7 +8525,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8728,7 +8731,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -8934,7 +8937,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9218,7 +9221,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ40">
         <v>1.38</v>
@@ -9427,7 +9430,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR41">
         <v>1.71</v>
@@ -9758,7 +9761,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9964,7 +9967,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10582,7 +10585,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10788,7 +10791,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10994,7 +10997,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11612,7 +11615,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12024,7 +12027,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12102,7 +12105,7 @@
         <v>0.67</v>
       </c>
       <c r="AP54">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ54">
         <v>0.88</v>
@@ -12230,7 +12233,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12642,7 +12645,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12848,7 +12851,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13054,7 +13057,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13672,7 +13675,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13753,7 +13756,7 @@
         <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR62">
         <v>1.7</v>
@@ -13878,7 +13881,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14084,7 +14087,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14368,7 +14371,7 @@
         <v>1.2</v>
       </c>
       <c r="AP65">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -14702,7 +14705,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -14908,7 +14911,7 @@
         <v>84</v>
       </c>
       <c r="P68" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>6.5</v>
@@ -15114,7 +15117,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15320,7 +15323,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15813,7 +15816,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ72">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR72">
         <v>1.28</v>
@@ -15938,7 +15941,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16350,7 +16353,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16556,7 +16559,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16968,7 +16971,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17174,7 +17177,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17380,7 +17383,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17792,7 +17795,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -17998,7 +18001,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18282,7 +18285,7 @@
         <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ84">
         <v>1.78</v>
@@ -18410,7 +18413,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18822,7 +18825,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19109,7 +19112,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR88">
         <v>1.86</v>
@@ -19440,7 +19443,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19646,7 +19649,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19852,7 +19855,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20136,7 +20139,7 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ93">
         <v>1.5</v>
@@ -20264,7 +20267,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20470,7 +20473,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20676,7 +20679,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -21088,7 +21091,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21294,7 +21297,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21912,7 +21915,7 @@
         <v>150</v>
       </c>
       <c r="P102" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -22324,7 +22327,7 @@
         <v>84</v>
       </c>
       <c r="P104" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q104">
         <v>7.5</v>
@@ -22736,7 +22739,7 @@
         <v>151</v>
       </c>
       <c r="P106" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q106">
         <v>8.5</v>
@@ -23020,7 +23023,7 @@
         <v>0.86</v>
       </c>
       <c r="AP107">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ107">
         <v>0.67</v>
@@ -23766,7 +23769,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -23972,7 +23975,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24053,7 +24056,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR112">
         <v>1.43</v>
@@ -24384,7 +24387,7 @@
         <v>157</v>
       </c>
       <c r="P114" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24796,7 +24799,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25002,7 +25005,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25208,7 +25211,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25414,7 +25417,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25620,7 +25623,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -25777,6 +25780,212 @@
       </c>
       <c r="BP120">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7537412</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45668.64583333334</v>
+      </c>
+      <c r="F121">
+        <v>18</v>
+      </c>
+      <c r="G121" t="s">
+        <v>80</v>
+      </c>
+      <c r="H121" t="s">
+        <v>82</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>2</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>3</v>
+      </c>
+      <c r="O121" t="s">
+        <v>161</v>
+      </c>
+      <c r="P121" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q121">
+        <v>1.83</v>
+      </c>
+      <c r="R121">
+        <v>2.4</v>
+      </c>
+      <c r="S121">
+        <v>8.5</v>
+      </c>
+      <c r="T121">
+        <v>1.36</v>
+      </c>
+      <c r="U121">
+        <v>3</v>
+      </c>
+      <c r="V121">
+        <v>2.63</v>
+      </c>
+      <c r="W121">
+        <v>1.44</v>
+      </c>
+      <c r="X121">
+        <v>7</v>
+      </c>
+      <c r="Y121">
+        <v>1.1</v>
+      </c>
+      <c r="Z121">
+        <v>1.28</v>
+      </c>
+      <c r="AA121">
+        <v>5.45</v>
+      </c>
+      <c r="AB121">
+        <v>11</v>
+      </c>
+      <c r="AC121">
+        <v>1.05</v>
+      </c>
+      <c r="AD121">
+        <v>7.2</v>
+      </c>
+      <c r="AE121">
+        <v>1.28</v>
+      </c>
+      <c r="AF121">
+        <v>3.5</v>
+      </c>
+      <c r="AG121">
+        <v>1.78</v>
+      </c>
+      <c r="AH121">
+        <v>1.9</v>
+      </c>
+      <c r="AI121">
+        <v>2.2</v>
+      </c>
+      <c r="AJ121">
+        <v>1.62</v>
+      </c>
+      <c r="AK121">
+        <v>1.07</v>
+      </c>
+      <c r="AL121">
+        <v>1.2</v>
+      </c>
+      <c r="AM121">
+        <v>3.15</v>
+      </c>
+      <c r="AN121">
+        <v>2.5</v>
+      </c>
+      <c r="AO121">
+        <v>1</v>
+      </c>
+      <c r="AP121">
+        <v>2.56</v>
+      </c>
+      <c r="AQ121">
+        <v>0.89</v>
+      </c>
+      <c r="AR121">
+        <v>1.96</v>
+      </c>
+      <c r="AS121">
+        <v>1.1</v>
+      </c>
+      <c r="AT121">
+        <v>3.06</v>
+      </c>
+      <c r="AU121">
+        <v>7</v>
+      </c>
+      <c r="AV121">
+        <v>3</v>
+      </c>
+      <c r="AW121">
+        <v>10</v>
+      </c>
+      <c r="AX121">
+        <v>1</v>
+      </c>
+      <c r="AY121">
+        <v>23</v>
+      </c>
+      <c r="AZ121">
+        <v>5</v>
+      </c>
+      <c r="BA121">
+        <v>6</v>
+      </c>
+      <c r="BB121">
+        <v>0</v>
+      </c>
+      <c r="BC121">
+        <v>6</v>
+      </c>
+      <c r="BD121">
+        <v>1.28</v>
+      </c>
+      <c r="BE121">
+        <v>7.5</v>
+      </c>
+      <c r="BF121">
+        <v>4.1</v>
+      </c>
+      <c r="BG121">
+        <v>1.37</v>
+      </c>
+      <c r="BH121">
+        <v>2.63</v>
+      </c>
+      <c r="BI121">
+        <v>1.64</v>
+      </c>
+      <c r="BJ121">
+        <v>2</v>
+      </c>
+      <c r="BK121">
+        <v>2.04</v>
+      </c>
+      <c r="BL121">
+        <v>1.61</v>
+      </c>
+      <c r="BM121">
+        <v>2.63</v>
+      </c>
+      <c r="BN121">
+        <v>1.37</v>
+      </c>
+      <c r="BO121">
+        <v>3.45</v>
+      </c>
+      <c r="BP121">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="233">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -502,6 +502,15 @@
     <t>['50', '90+6']</t>
   </si>
   <si>
+    <t>['64', '76']</t>
+  </si>
+  <si>
+    <t>['69']</t>
+  </si>
+  <si>
+    <t>['18', '90+3']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -679,9 +688,6 @@
     <t>['88']</t>
   </si>
   <si>
-    <t>['69']</t>
-  </si>
-  <si>
     <t>['57']</t>
   </si>
   <si>
@@ -698,6 +704,15 @@
   </si>
   <si>
     <t>['45+5', '70']</t>
+  </si>
+  <si>
+    <t>['38', '48']</t>
+  </si>
+  <si>
+    <t>['5', '19', '51']</t>
+  </si>
+  <si>
+    <t>['90+2', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1315,7 +1330,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1521,7 +1536,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -1599,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -1808,7 +1823,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ4">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2139,7 +2154,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2423,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ7">
         <v>1.67</v>
@@ -2551,7 +2566,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2838,7 +2853,7 @@
         <v>1</v>
       </c>
       <c r="AQ9">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2963,7 +2978,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3169,7 +3184,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3247,7 +3262,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ11">
         <v>0.67</v>
@@ -3375,7 +3390,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3456,7 +3471,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ12">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3659,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ13">
         <v>1.63</v>
@@ -3993,7 +4008,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q15">
         <v>1.44</v>
@@ -4074,7 +4089,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ15">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4199,7 +4214,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4277,7 +4292,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ16">
         <v>1.89</v>
@@ -4405,7 +4420,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4817,7 +4832,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5023,7 +5038,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5229,7 +5244,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5435,7 +5450,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5516,7 +5531,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ22">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5719,10 +5734,10 @@
         <v>0.5</v>
       </c>
       <c r="AP23">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ23">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR23">
         <v>0.92</v>
@@ -5847,7 +5862,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -5928,7 +5943,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ24">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR24">
         <v>2.26</v>
@@ -6053,7 +6068,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6543,10 +6558,10 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ27">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR27">
         <v>1.95</v>
@@ -6671,7 +6686,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6955,10 +6970,10 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ29">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR29">
         <v>2.28</v>
@@ -7083,7 +7098,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7495,7 +7510,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7907,7 +7922,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8113,7 +8128,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8525,7 +8540,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8606,7 +8621,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ37">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR37">
         <v>1.17</v>
@@ -8731,7 +8746,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -8937,7 +8952,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9224,7 +9239,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ40">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR40">
         <v>2.09</v>
@@ -9427,7 +9442,7 @@
         <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41">
         <v>0.89</v>
@@ -9633,10 +9648,10 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ42">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR42">
         <v>1.99</v>
@@ -9761,7 +9776,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9839,7 +9854,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -9967,7 +9982,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10048,7 +10063,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ44">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR44">
         <v>1.35</v>
@@ -10585,7 +10600,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10791,7 +10806,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10997,7 +11012,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11615,7 +11630,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -11899,7 +11914,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -12027,7 +12042,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12233,7 +12248,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12314,7 +12329,7 @@
         <v>1</v>
       </c>
       <c r="AQ55">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR55">
         <v>1.16</v>
@@ -12520,7 +12535,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ56">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR56">
         <v>1.14</v>
@@ -12645,7 +12660,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12723,7 +12738,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ57">
         <v>2.44</v>
@@ -12851,7 +12866,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -12932,7 +12947,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ58">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR58">
         <v>1.3</v>
@@ -13057,7 +13072,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13675,7 +13690,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13881,7 +13896,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -13959,7 +13974,7 @@
         <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ63">
         <v>1.67</v>
@@ -14087,7 +14102,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14168,7 +14183,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ64">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR64">
         <v>1.31</v>
@@ -14705,7 +14720,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -14911,7 +14926,7 @@
         <v>84</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q68">
         <v>6.5</v>
@@ -14992,7 +15007,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ68">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR68">
         <v>1.45</v>
@@ -15117,7 +15132,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15323,7 +15338,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15401,7 +15416,7 @@
         <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ70">
         <v>2.44</v>
@@ -15941,7 +15956,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16022,7 +16037,7 @@
         <v>1</v>
       </c>
       <c r="AQ73">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR73">
         <v>1.13</v>
@@ -16225,7 +16240,7 @@
         <v>1.8</v>
       </c>
       <c r="AP74">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ74">
         <v>1.33</v>
@@ -16353,7 +16368,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16434,7 +16449,7 @@
         <v>1</v>
       </c>
       <c r="AQ75">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR75">
         <v>1.19</v>
@@ -16559,7 +16574,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16640,7 +16655,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ76">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR76">
         <v>1.06</v>
@@ -16971,7 +16986,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17049,7 +17064,7 @@
         <v>1.4</v>
       </c>
       <c r="AP78">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ78">
         <v>1.89</v>
@@ -17177,7 +17192,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17383,7 +17398,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17461,7 +17476,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ80">
         <v>1.67</v>
@@ -17670,7 +17685,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR81">
         <v>1.51</v>
@@ -17795,7 +17810,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -17876,7 +17891,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ82">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR82">
         <v>1.27</v>
@@ -18001,7 +18016,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18413,7 +18428,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18825,7 +18840,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19109,7 +19124,7 @@
         <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ88">
         <v>0.89</v>
@@ -19443,7 +19458,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19649,7 +19664,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19727,10 +19742,10 @@
         <v>0.67</v>
       </c>
       <c r="AP91">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ91">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR91">
         <v>1.68</v>
@@ -19855,7 +19870,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -19936,7 +19951,7 @@
         <v>2</v>
       </c>
       <c r="AQ92">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR92">
         <v>1.7</v>
@@ -20142,7 +20157,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ93">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR93">
         <v>1.95</v>
@@ -20267,7 +20282,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20348,7 +20363,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ94">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR94">
         <v>1.56</v>
@@ -20473,7 +20488,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20679,7 +20694,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -20966,7 +20981,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ97">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR97">
         <v>1.4</v>
@@ -21091,7 +21106,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21169,7 +21184,7 @@
         <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ98">
         <v>1.63</v>
@@ -21297,7 +21312,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21581,7 +21596,7 @@
         <v>1.43</v>
       </c>
       <c r="AP100">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ100">
         <v>1.78</v>
@@ -21915,7 +21930,7 @@
         <v>150</v>
       </c>
       <c r="P102" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -22327,7 +22342,7 @@
         <v>84</v>
       </c>
       <c r="P104" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q104">
         <v>7.5</v>
@@ -22408,7 +22423,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ104">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR104">
         <v>1.19</v>
@@ -22739,7 +22754,7 @@
         <v>151</v>
       </c>
       <c r="P106" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="Q106">
         <v>8.5</v>
@@ -23438,7 +23453,7 @@
         <v>2</v>
       </c>
       <c r="AQ109">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR109">
         <v>1.74</v>
@@ -23641,10 +23656,10 @@
         <v>1.57</v>
       </c>
       <c r="AP110">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ110">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR110">
         <v>1.66</v>
@@ -23769,7 +23784,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -23847,7 +23862,7 @@
         <v>0.86</v>
       </c>
       <c r="AP111">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ111">
         <v>0.88</v>
@@ -23975,7 +23990,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24262,7 +24277,7 @@
         <v>1</v>
       </c>
       <c r="AQ113">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR113">
         <v>1.13</v>
@@ -24387,7 +24402,7 @@
         <v>157</v>
       </c>
       <c r="P114" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24799,7 +24814,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25005,7 +25020,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25211,7 +25226,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25417,7 +25432,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25623,7 +25638,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -25922,22 +25937,22 @@
         <v>3.06</v>
       </c>
       <c r="AU121">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV121">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW121">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY121">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AZ121">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA121">
         <v>6</v>
@@ -25986,6 +26001,830 @@
       </c>
       <c r="BP121">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7537414</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45669.47916666666</v>
+      </c>
+      <c r="F122">
+        <v>18</v>
+      </c>
+      <c r="G122" t="s">
+        <v>78</v>
+      </c>
+      <c r="H122" t="s">
+        <v>73</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="K122">
+        <v>1</v>
+      </c>
+      <c r="L122">
+        <v>2</v>
+      </c>
+      <c r="M122">
+        <v>2</v>
+      </c>
+      <c r="N122">
+        <v>4</v>
+      </c>
+      <c r="O122" t="s">
+        <v>162</v>
+      </c>
+      <c r="P122" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q122">
+        <v>7</v>
+      </c>
+      <c r="R122">
+        <v>2.25</v>
+      </c>
+      <c r="S122">
+        <v>2</v>
+      </c>
+      <c r="T122">
+        <v>1.4</v>
+      </c>
+      <c r="U122">
+        <v>2.75</v>
+      </c>
+      <c r="V122">
+        <v>2.75</v>
+      </c>
+      <c r="W122">
+        <v>1.4</v>
+      </c>
+      <c r="X122">
+        <v>8</v>
+      </c>
+      <c r="Y122">
+        <v>1.08</v>
+      </c>
+      <c r="Z122">
+        <v>7</v>
+      </c>
+      <c r="AA122">
+        <v>4.5</v>
+      </c>
+      <c r="AB122">
+        <v>1.4</v>
+      </c>
+      <c r="AC122">
+        <v>1.05</v>
+      </c>
+      <c r="AD122">
+        <v>6.8</v>
+      </c>
+      <c r="AE122">
+        <v>1.28</v>
+      </c>
+      <c r="AF122">
+        <v>3.55</v>
+      </c>
+      <c r="AG122">
+        <v>1.85</v>
+      </c>
+      <c r="AH122">
+        <v>1.8</v>
+      </c>
+      <c r="AI122">
+        <v>2.1</v>
+      </c>
+      <c r="AJ122">
+        <v>1.67</v>
+      </c>
+      <c r="AK122">
+        <v>2.75</v>
+      </c>
+      <c r="AL122">
+        <v>1.23</v>
+      </c>
+      <c r="AM122">
+        <v>1.1</v>
+      </c>
+      <c r="AN122">
+        <v>1</v>
+      </c>
+      <c r="AO122">
+        <v>2.13</v>
+      </c>
+      <c r="AP122">
+        <v>1</v>
+      </c>
+      <c r="AQ122">
+        <v>2</v>
+      </c>
+      <c r="AR122">
+        <v>1.28</v>
+      </c>
+      <c r="AS122">
+        <v>1.51</v>
+      </c>
+      <c r="AT122">
+        <v>2.79</v>
+      </c>
+      <c r="AU122">
+        <v>4</v>
+      </c>
+      <c r="AV122">
+        <v>6</v>
+      </c>
+      <c r="AW122">
+        <v>4</v>
+      </c>
+      <c r="AX122">
+        <v>5</v>
+      </c>
+      <c r="AY122">
+        <v>11</v>
+      </c>
+      <c r="AZ122">
+        <v>13</v>
+      </c>
+      <c r="BA122">
+        <v>1</v>
+      </c>
+      <c r="BB122">
+        <v>6</v>
+      </c>
+      <c r="BC122">
+        <v>7</v>
+      </c>
+      <c r="BD122">
+        <v>3.8</v>
+      </c>
+      <c r="BE122">
+        <v>7</v>
+      </c>
+      <c r="BF122">
+        <v>1.32</v>
+      </c>
+      <c r="BG122">
+        <v>1.4</v>
+      </c>
+      <c r="BH122">
+        <v>2.55</v>
+      </c>
+      <c r="BI122">
+        <v>1.68</v>
+      </c>
+      <c r="BJ122">
+        <v>1.94</v>
+      </c>
+      <c r="BK122">
+        <v>2.1</v>
+      </c>
+      <c r="BL122">
+        <v>1.58</v>
+      </c>
+      <c r="BM122">
+        <v>2.7</v>
+      </c>
+      <c r="BN122">
+        <v>1.35</v>
+      </c>
+      <c r="BO122">
+        <v>3.6</v>
+      </c>
+      <c r="BP122">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7537416</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45669.5</v>
+      </c>
+      <c r="F123">
+        <v>18</v>
+      </c>
+      <c r="G123" t="s">
+        <v>81</v>
+      </c>
+      <c r="H123" t="s">
+        <v>74</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>2</v>
+      </c>
+      <c r="K123">
+        <v>2</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>3</v>
+      </c>
+      <c r="N123">
+        <v>3</v>
+      </c>
+      <c r="O123" t="s">
+        <v>84</v>
+      </c>
+      <c r="P123" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q123">
+        <v>4.33</v>
+      </c>
+      <c r="R123">
+        <v>1.91</v>
+      </c>
+      <c r="S123">
+        <v>3</v>
+      </c>
+      <c r="T123">
+        <v>1.57</v>
+      </c>
+      <c r="U123">
+        <v>2.25</v>
+      </c>
+      <c r="V123">
+        <v>3.75</v>
+      </c>
+      <c r="W123">
+        <v>1.25</v>
+      </c>
+      <c r="X123">
+        <v>13</v>
+      </c>
+      <c r="Y123">
+        <v>1.04</v>
+      </c>
+      <c r="Z123">
+        <v>3.6</v>
+      </c>
+      <c r="AA123">
+        <v>2.9</v>
+      </c>
+      <c r="AB123">
+        <v>2.15</v>
+      </c>
+      <c r="AC123">
+        <v>1.11</v>
+      </c>
+      <c r="AD123">
+        <v>6.8</v>
+      </c>
+      <c r="AE123">
+        <v>1.52</v>
+      </c>
+      <c r="AF123">
+        <v>2.55</v>
+      </c>
+      <c r="AG123">
+        <v>2.3</v>
+      </c>
+      <c r="AH123">
+        <v>1.5</v>
+      </c>
+      <c r="AI123">
+        <v>2.1</v>
+      </c>
+      <c r="AJ123">
+        <v>1.67</v>
+      </c>
+      <c r="AK123">
+        <v>1.72</v>
+      </c>
+      <c r="AL123">
+        <v>1.38</v>
+      </c>
+      <c r="AM123">
+        <v>1.32</v>
+      </c>
+      <c r="AN123">
+        <v>0.38</v>
+      </c>
+      <c r="AO123">
+        <v>1.38</v>
+      </c>
+      <c r="AP123">
+        <v>0.33</v>
+      </c>
+      <c r="AQ123">
+        <v>1.56</v>
+      </c>
+      <c r="AR123">
+        <v>1.09</v>
+      </c>
+      <c r="AS123">
+        <v>1.05</v>
+      </c>
+      <c r="AT123">
+        <v>2.14</v>
+      </c>
+      <c r="AU123">
+        <v>3</v>
+      </c>
+      <c r="AV123">
+        <v>6</v>
+      </c>
+      <c r="AW123">
+        <v>9</v>
+      </c>
+      <c r="AX123">
+        <v>3</v>
+      </c>
+      <c r="AY123">
+        <v>12</v>
+      </c>
+      <c r="AZ123">
+        <v>9</v>
+      </c>
+      <c r="BA123">
+        <v>6</v>
+      </c>
+      <c r="BB123">
+        <v>1</v>
+      </c>
+      <c r="BC123">
+        <v>7</v>
+      </c>
+      <c r="BD123">
+        <v>2.48</v>
+      </c>
+      <c r="BE123">
+        <v>6.6</v>
+      </c>
+      <c r="BF123">
+        <v>1.75</v>
+      </c>
+      <c r="BG123">
+        <v>1.46</v>
+      </c>
+      <c r="BH123">
+        <v>2.45</v>
+      </c>
+      <c r="BI123">
+        <v>1.85</v>
+      </c>
+      <c r="BJ123">
+        <v>1.95</v>
+      </c>
+      <c r="BK123">
+        <v>2.45</v>
+      </c>
+      <c r="BL123">
+        <v>1.44</v>
+      </c>
+      <c r="BM123">
+        <v>3.5</v>
+      </c>
+      <c r="BN123">
+        <v>1.24</v>
+      </c>
+      <c r="BO123">
+        <v>4</v>
+      </c>
+      <c r="BP123">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7537415</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45669.60416666666</v>
+      </c>
+      <c r="F124">
+        <v>18</v>
+      </c>
+      <c r="G124" t="s">
+        <v>71</v>
+      </c>
+      <c r="H124" t="s">
+        <v>70</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <v>2</v>
+      </c>
+      <c r="N124">
+        <v>3</v>
+      </c>
+      <c r="O124" t="s">
+        <v>163</v>
+      </c>
+      <c r="P124" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q124">
+        <v>1.62</v>
+      </c>
+      <c r="R124">
+        <v>2.63</v>
+      </c>
+      <c r="S124">
+        <v>11</v>
+      </c>
+      <c r="T124">
+        <v>1.3</v>
+      </c>
+      <c r="U124">
+        <v>3.4</v>
+      </c>
+      <c r="V124">
+        <v>2.38</v>
+      </c>
+      <c r="W124">
+        <v>1.53</v>
+      </c>
+      <c r="X124">
+        <v>6</v>
+      </c>
+      <c r="Y124">
+        <v>1.13</v>
+      </c>
+      <c r="Z124">
+        <v>1.17</v>
+      </c>
+      <c r="AA124">
+        <v>6.5</v>
+      </c>
+      <c r="AB124">
+        <v>13</v>
+      </c>
+      <c r="AC124">
+        <v>1</v>
+      </c>
+      <c r="AD124">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE124">
+        <v>1.2</v>
+      </c>
+      <c r="AF124">
+        <v>4.6</v>
+      </c>
+      <c r="AG124">
+        <v>1.6</v>
+      </c>
+      <c r="AH124">
+        <v>2.1</v>
+      </c>
+      <c r="AI124">
+        <v>2.25</v>
+      </c>
+      <c r="AJ124">
+        <v>1.57</v>
+      </c>
+      <c r="AK124">
+        <v>1.06</v>
+      </c>
+      <c r="AL124">
+        <v>1.14</v>
+      </c>
+      <c r="AM124">
+        <v>4.2</v>
+      </c>
+      <c r="AN124">
+        <v>1.38</v>
+      </c>
+      <c r="AO124">
+        <v>1.5</v>
+      </c>
+      <c r="AP124">
+        <v>1.22</v>
+      </c>
+      <c r="AQ124">
+        <v>1.67</v>
+      </c>
+      <c r="AR124">
+        <v>1.66</v>
+      </c>
+      <c r="AS124">
+        <v>0.88</v>
+      </c>
+      <c r="AT124">
+        <v>2.54</v>
+      </c>
+      <c r="AU124">
+        <v>6</v>
+      </c>
+      <c r="AV124">
+        <v>8</v>
+      </c>
+      <c r="AW124">
+        <v>11</v>
+      </c>
+      <c r="AX124">
+        <v>2</v>
+      </c>
+      <c r="AY124">
+        <v>21</v>
+      </c>
+      <c r="AZ124">
+        <v>10</v>
+      </c>
+      <c r="BA124">
+        <v>15</v>
+      </c>
+      <c r="BB124">
+        <v>3</v>
+      </c>
+      <c r="BC124">
+        <v>18</v>
+      </c>
+      <c r="BD124">
+        <v>1.13</v>
+      </c>
+      <c r="BE124">
+        <v>9</v>
+      </c>
+      <c r="BF124">
+        <v>6.4</v>
+      </c>
+      <c r="BG124">
+        <v>1.42</v>
+      </c>
+      <c r="BH124">
+        <v>2.45</v>
+      </c>
+      <c r="BI124">
+        <v>1.71</v>
+      </c>
+      <c r="BJ124">
+        <v>1.89</v>
+      </c>
+      <c r="BK124">
+        <v>2.14</v>
+      </c>
+      <c r="BL124">
+        <v>1.55</v>
+      </c>
+      <c r="BM124">
+        <v>2.75</v>
+      </c>
+      <c r="BN124">
+        <v>1.33</v>
+      </c>
+      <c r="BO124">
+        <v>3.65</v>
+      </c>
+      <c r="BP124">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7537410</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45669.64583333334</v>
+      </c>
+      <c r="F125">
+        <v>18</v>
+      </c>
+      <c r="G125" t="s">
+        <v>75</v>
+      </c>
+      <c r="H125" t="s">
+        <v>83</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>2</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>2</v>
+      </c>
+      <c r="O125" t="s">
+        <v>164</v>
+      </c>
+      <c r="P125" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q125">
+        <v>1.5</v>
+      </c>
+      <c r="R125">
+        <v>2.88</v>
+      </c>
+      <c r="S125">
+        <v>13</v>
+      </c>
+      <c r="T125">
+        <v>1.25</v>
+      </c>
+      <c r="U125">
+        <v>3.75</v>
+      </c>
+      <c r="V125">
+        <v>2.2</v>
+      </c>
+      <c r="W125">
+        <v>1.62</v>
+      </c>
+      <c r="X125">
+        <v>5</v>
+      </c>
+      <c r="Y125">
+        <v>1.17</v>
+      </c>
+      <c r="Z125">
+        <v>1.18</v>
+      </c>
+      <c r="AA125">
+        <v>6</v>
+      </c>
+      <c r="AB125">
+        <v>13</v>
+      </c>
+      <c r="AC125">
+        <v>1.01</v>
+      </c>
+      <c r="AD125">
+        <v>17</v>
+      </c>
+      <c r="AE125">
+        <v>1.16</v>
+      </c>
+      <c r="AF125">
+        <v>5.4</v>
+      </c>
+      <c r="AG125">
+        <v>1.53</v>
+      </c>
+      <c r="AH125">
+        <v>2.29</v>
+      </c>
+      <c r="AI125">
+        <v>2.38</v>
+      </c>
+      <c r="AJ125">
+        <v>1.53</v>
+      </c>
+      <c r="AK125">
+        <v>1.04</v>
+      </c>
+      <c r="AL125">
+        <v>1.1</v>
+      </c>
+      <c r="AM125">
+        <v>5.2</v>
+      </c>
+      <c r="AN125">
+        <v>2.25</v>
+      </c>
+      <c r="AO125">
+        <v>0.63</v>
+      </c>
+      <c r="AP125">
+        <v>2.33</v>
+      </c>
+      <c r="AQ125">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR125">
+        <v>1.95</v>
+      </c>
+      <c r="AS125">
+        <v>0.87</v>
+      </c>
+      <c r="AT125">
+        <v>2.82</v>
+      </c>
+      <c r="AU125">
+        <v>6</v>
+      </c>
+      <c r="AV125">
+        <v>3</v>
+      </c>
+      <c r="AW125">
+        <v>21</v>
+      </c>
+      <c r="AX125">
+        <v>4</v>
+      </c>
+      <c r="AY125">
+        <v>36</v>
+      </c>
+      <c r="AZ125">
+        <v>8</v>
+      </c>
+      <c r="BA125">
+        <v>9</v>
+      </c>
+      <c r="BB125">
+        <v>3</v>
+      </c>
+      <c r="BC125">
+        <v>12</v>
+      </c>
+      <c r="BD125">
+        <v>1.16</v>
+      </c>
+      <c r="BE125">
+        <v>9</v>
+      </c>
+      <c r="BF125">
+        <v>5.6</v>
+      </c>
+      <c r="BG125">
+        <v>1.33</v>
+      </c>
+      <c r="BH125">
+        <v>2.75</v>
+      </c>
+      <c r="BI125">
+        <v>1.58</v>
+      </c>
+      <c r="BJ125">
+        <v>2.08</v>
+      </c>
+      <c r="BK125">
+        <v>1.95</v>
+      </c>
+      <c r="BL125">
+        <v>1.67</v>
+      </c>
+      <c r="BM125">
+        <v>2.48</v>
+      </c>
+      <c r="BN125">
+        <v>1.41</v>
+      </c>
+      <c r="BO125">
+        <v>3.2</v>
+      </c>
+      <c r="BP125">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="234">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -509,6 +509,9 @@
   </si>
   <si>
     <t>['18', '90+3']</t>
+  </si>
+  <si>
+    <t>['46', '60']</t>
   </si>
   <si>
     <t>['13', '73']</t>
@@ -1074,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP125"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1330,7 +1333,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1536,7 +1539,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -2154,7 +2157,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2566,7 +2569,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2978,7 +2981,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3184,7 +3187,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3390,7 +3393,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3468,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ12">
         <v>1.67</v>
@@ -3677,7 +3680,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ13">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR13">
         <v>1.83</v>
@@ -3883,7 +3886,7 @@
         <v>2</v>
       </c>
       <c r="AQ14">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
@@ -4008,7 +4011,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q15">
         <v>1.44</v>
@@ -4214,7 +4217,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4420,7 +4423,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4832,7 +4835,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5038,7 +5041,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5244,7 +5247,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5450,7 +5453,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5862,7 +5865,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -5940,7 +5943,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ24">
         <v>1.56</v>
@@ -6068,7 +6071,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6149,7 +6152,7 @@
         <v>1</v>
       </c>
       <c r="AQ25">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR25">
         <v>0.98</v>
@@ -6355,7 +6358,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ26">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR26">
         <v>1.48</v>
@@ -6686,7 +6689,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7098,7 +7101,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7510,7 +7513,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7922,7 +7925,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8128,7 +8131,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8540,7 +8543,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8746,7 +8749,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -8824,10 +8827,10 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ38">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -8952,7 +8955,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9033,7 +9036,7 @@
         <v>1</v>
       </c>
       <c r="AQ39">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR39">
         <v>1.2</v>
@@ -9776,7 +9779,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9982,7 +9985,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10600,7 +10603,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10806,7 +10809,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11012,7 +11015,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11630,7 +11633,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -11711,7 +11714,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ52">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR52">
         <v>1.4</v>
@@ -12042,7 +12045,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12123,7 +12126,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ54">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR54">
         <v>2.03</v>
@@ -12248,7 +12251,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12660,7 +12663,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12866,7 +12869,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13072,7 +13075,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13562,7 +13565,7 @@
         <v>1.75</v>
       </c>
       <c r="AP61">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ61">
         <v>1.89</v>
@@ -13690,7 +13693,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13896,7 +13899,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14102,7 +14105,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14595,7 +14598,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ66">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR66">
         <v>1.31</v>
@@ -14720,7 +14723,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -14801,7 +14804,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ67">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR67">
         <v>1.46</v>
@@ -14926,7 +14929,7 @@
         <v>84</v>
       </c>
       <c r="P68" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q68">
         <v>6.5</v>
@@ -15132,7 +15135,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15338,7 +15341,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15622,7 +15625,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ71">
         <v>1.67</v>
@@ -15956,7 +15959,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16368,7 +16371,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16574,7 +16577,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16986,7 +16989,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17192,7 +17195,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17398,7 +17401,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17810,7 +17813,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18016,7 +18019,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18094,7 +18097,7 @@
         <v>2.6</v>
       </c>
       <c r="AP83">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ83">
         <v>2.44</v>
@@ -18428,7 +18431,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18509,7 +18512,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ85">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR85">
         <v>1.32</v>
@@ -18840,7 +18843,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -18921,7 +18924,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ87">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR87">
         <v>1.2</v>
@@ -19458,7 +19461,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19664,7 +19667,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19870,7 +19873,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20282,7 +20285,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20488,7 +20491,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20694,7 +20697,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -20978,7 +20981,7 @@
         <v>1.83</v>
       </c>
       <c r="AP97">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ97">
         <v>2</v>
@@ -21106,7 +21109,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21187,7 +21190,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ98">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR98">
         <v>1.1</v>
@@ -21312,7 +21315,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21393,7 +21396,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ99">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR99">
         <v>1.5</v>
@@ -21930,7 +21933,7 @@
         <v>150</v>
       </c>
       <c r="P102" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -22342,7 +22345,7 @@
         <v>84</v>
       </c>
       <c r="P104" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q104">
         <v>7.5</v>
@@ -23247,7 +23250,7 @@
         <v>1</v>
       </c>
       <c r="AQ108">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR108">
         <v>1.22</v>
@@ -23784,7 +23787,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -23865,7 +23868,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ111">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR111">
         <v>1.89</v>
@@ -23990,7 +23993,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24068,7 +24071,7 @@
         <v>1.14</v>
       </c>
       <c r="AP112">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ112">
         <v>0.89</v>
@@ -24814,7 +24817,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25020,7 +25023,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25226,7 +25229,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25432,7 +25435,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25638,7 +25641,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -26050,7 +26053,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26256,7 +26259,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26462,7 +26465,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26825,6 +26828,418 @@
       </c>
       <c r="BP125">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7537411</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45670.54166666666</v>
+      </c>
+      <c r="F126">
+        <v>18</v>
+      </c>
+      <c r="G126" t="s">
+        <v>79</v>
+      </c>
+      <c r="H126" t="s">
+        <v>76</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>2</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>2</v>
+      </c>
+      <c r="O126" t="s">
+        <v>165</v>
+      </c>
+      <c r="P126" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q126">
+        <v>2.88</v>
+      </c>
+      <c r="R126">
+        <v>1.91</v>
+      </c>
+      <c r="S126">
+        <v>4.5</v>
+      </c>
+      <c r="T126">
+        <v>1.57</v>
+      </c>
+      <c r="U126">
+        <v>2.25</v>
+      </c>
+      <c r="V126">
+        <v>3.75</v>
+      </c>
+      <c r="W126">
+        <v>1.25</v>
+      </c>
+      <c r="X126">
+        <v>13</v>
+      </c>
+      <c r="Y126">
+        <v>1.04</v>
+      </c>
+      <c r="Z126">
+        <v>2.32</v>
+      </c>
+      <c r="AA126">
+        <v>3.14</v>
+      </c>
+      <c r="AB126">
+        <v>3.32</v>
+      </c>
+      <c r="AC126">
+        <v>1.11</v>
+      </c>
+      <c r="AD126">
+        <v>4.4</v>
+      </c>
+      <c r="AE126">
+        <v>1.5</v>
+      </c>
+      <c r="AF126">
+        <v>2.4</v>
+      </c>
+      <c r="AG126">
+        <v>2.4</v>
+      </c>
+      <c r="AH126">
+        <v>1.46</v>
+      </c>
+      <c r="AI126">
+        <v>2.1</v>
+      </c>
+      <c r="AJ126">
+        <v>1.67</v>
+      </c>
+      <c r="AK126">
+        <v>1.27</v>
+      </c>
+      <c r="AL126">
+        <v>1.38</v>
+      </c>
+      <c r="AM126">
+        <v>1.74</v>
+      </c>
+      <c r="AN126">
+        <v>1.25</v>
+      </c>
+      <c r="AO126">
+        <v>1.63</v>
+      </c>
+      <c r="AP126">
+        <v>1.44</v>
+      </c>
+      <c r="AQ126">
+        <v>1.44</v>
+      </c>
+      <c r="AR126">
+        <v>1.41</v>
+      </c>
+      <c r="AS126">
+        <v>0.92</v>
+      </c>
+      <c r="AT126">
+        <v>2.33</v>
+      </c>
+      <c r="AU126">
+        <v>5</v>
+      </c>
+      <c r="AV126">
+        <v>6</v>
+      </c>
+      <c r="AW126">
+        <v>5</v>
+      </c>
+      <c r="AX126">
+        <v>6</v>
+      </c>
+      <c r="AY126">
+        <v>11</v>
+      </c>
+      <c r="AZ126">
+        <v>14</v>
+      </c>
+      <c r="BA126">
+        <v>4</v>
+      </c>
+      <c r="BB126">
+        <v>4</v>
+      </c>
+      <c r="BC126">
+        <v>8</v>
+      </c>
+      <c r="BD126">
+        <v>1.68</v>
+      </c>
+      <c r="BE126">
+        <v>6.4</v>
+      </c>
+      <c r="BF126">
+        <v>2.43</v>
+      </c>
+      <c r="BG126">
+        <v>1.49</v>
+      </c>
+      <c r="BH126">
+        <v>2.25</v>
+      </c>
+      <c r="BI126">
+        <v>1.86</v>
+      </c>
+      <c r="BJ126">
+        <v>1.75</v>
+      </c>
+      <c r="BK126">
+        <v>2.38</v>
+      </c>
+      <c r="BL126">
+        <v>1.45</v>
+      </c>
+      <c r="BM126">
+        <v>3.15</v>
+      </c>
+      <c r="BN126">
+        <v>1.26</v>
+      </c>
+      <c r="BO126">
+        <v>4.3</v>
+      </c>
+      <c r="BP126">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7537413</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45670.54166666666</v>
+      </c>
+      <c r="F127">
+        <v>18</v>
+      </c>
+      <c r="G127" t="s">
+        <v>77</v>
+      </c>
+      <c r="H127" t="s">
+        <v>72</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127" t="s">
+        <v>84</v>
+      </c>
+      <c r="P127" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q127">
+        <v>2.88</v>
+      </c>
+      <c r="R127">
+        <v>2</v>
+      </c>
+      <c r="S127">
+        <v>4.33</v>
+      </c>
+      <c r="T127">
+        <v>1.5</v>
+      </c>
+      <c r="U127">
+        <v>2.5</v>
+      </c>
+      <c r="V127">
+        <v>3.4</v>
+      </c>
+      <c r="W127">
+        <v>1.3</v>
+      </c>
+      <c r="X127">
+        <v>10</v>
+      </c>
+      <c r="Y127">
+        <v>1.06</v>
+      </c>
+      <c r="Z127">
+        <v>1.95</v>
+      </c>
+      <c r="AA127">
+        <v>3.56</v>
+      </c>
+      <c r="AB127">
+        <v>3.86</v>
+      </c>
+      <c r="AC127">
+        <v>1.08</v>
+      </c>
+      <c r="AD127">
+        <v>7.8</v>
+      </c>
+      <c r="AE127">
+        <v>1.41</v>
+      </c>
+      <c r="AF127">
+        <v>2.95</v>
+      </c>
+      <c r="AG127">
+        <v>1.96</v>
+      </c>
+      <c r="AH127">
+        <v>1.75</v>
+      </c>
+      <c r="AI127">
+        <v>1.95</v>
+      </c>
+      <c r="AJ127">
+        <v>1.8</v>
+      </c>
+      <c r="AK127">
+        <v>1.32</v>
+      </c>
+      <c r="AL127">
+        <v>1.37</v>
+      </c>
+      <c r="AM127">
+        <v>1.75</v>
+      </c>
+      <c r="AN127">
+        <v>1</v>
+      </c>
+      <c r="AO127">
+        <v>0.88</v>
+      </c>
+      <c r="AP127">
+        <v>1</v>
+      </c>
+      <c r="AQ127">
+        <v>0.89</v>
+      </c>
+      <c r="AR127">
+        <v>1.2</v>
+      </c>
+      <c r="AS127">
+        <v>1.04</v>
+      </c>
+      <c r="AT127">
+        <v>2.24</v>
+      </c>
+      <c r="AU127">
+        <v>7</v>
+      </c>
+      <c r="AV127">
+        <v>4</v>
+      </c>
+      <c r="AW127">
+        <v>15</v>
+      </c>
+      <c r="AX127">
+        <v>6</v>
+      </c>
+      <c r="AY127">
+        <v>27</v>
+      </c>
+      <c r="AZ127">
+        <v>11</v>
+      </c>
+      <c r="BA127">
+        <v>3</v>
+      </c>
+      <c r="BB127">
+        <v>5</v>
+      </c>
+      <c r="BC127">
+        <v>8</v>
+      </c>
+      <c r="BD127">
+        <v>1.96</v>
+      </c>
+      <c r="BE127">
+        <v>6.15</v>
+      </c>
+      <c r="BF127">
+        <v>2.42</v>
+      </c>
+      <c r="BG127">
+        <v>1.53</v>
+      </c>
+      <c r="BH127">
+        <v>2.28</v>
+      </c>
+      <c r="BI127">
+        <v>1.96</v>
+      </c>
+      <c r="BJ127">
+        <v>1.75</v>
+      </c>
+      <c r="BK127">
+        <v>2.6</v>
+      </c>
+      <c r="BL127">
+        <v>1.41</v>
+      </c>
+      <c r="BM127">
+        <v>3.58</v>
+      </c>
+      <c r="BN127">
+        <v>1.21</v>
+      </c>
+      <c r="BO127">
+        <v>5</v>
+      </c>
+      <c r="BP127">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -512,6 +512,9 @@
   </si>
   <si>
     <t>['46', '60']</t>
+  </si>
+  <si>
+    <t>['73', '90+4']</t>
   </si>
   <si>
     <t>['13', '73']</t>
@@ -1077,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1333,7 +1336,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1539,7 +1542,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -2157,7 +2160,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2569,7 +2572,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2981,7 +2984,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3187,7 +3190,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3393,7 +3396,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3474,7 +3477,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ12">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4011,7 +4014,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q15">
         <v>1.44</v>
@@ -4217,7 +4220,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4423,7 +4426,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4835,7 +4838,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5041,7 +5044,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5247,7 +5250,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5453,7 +5456,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5531,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
         <v>2</v>
@@ -5865,7 +5868,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6071,7 +6074,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6689,7 +6692,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6976,7 +6979,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ29">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR29">
         <v>2.28</v>
@@ -7101,7 +7104,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7513,7 +7516,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7925,7 +7928,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8131,7 +8134,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8415,7 +8418,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
         <v>1.78</v>
@@ -8543,7 +8546,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8749,7 +8752,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -8955,7 +8958,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9779,7 +9782,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9985,7 +9988,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10066,7 +10069,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ44">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR44">
         <v>1.35</v>
@@ -10603,7 +10606,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10809,7 +10812,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10887,7 +10890,7 @@
         <v>1.67</v>
       </c>
       <c r="AP48">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ48">
         <v>1.33</v>
@@ -11015,7 +11018,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11633,7 +11636,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12045,7 +12048,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12251,7 +12254,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12663,7 +12666,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12869,7 +12872,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -12950,7 +12953,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ58">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR58">
         <v>1.3</v>
@@ -13075,7 +13078,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13693,7 +13696,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13899,7 +13902,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14105,7 +14108,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14183,7 +14186,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ64">
         <v>1.56</v>
@@ -14595,7 +14598,7 @@
         <v>1.75</v>
       </c>
       <c r="AP66">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ66">
         <v>1.44</v>
@@ -14723,7 +14726,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -14929,7 +14932,7 @@
         <v>84</v>
       </c>
       <c r="P68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q68">
         <v>6.5</v>
@@ -15135,7 +15138,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15341,7 +15344,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15959,7 +15962,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16371,7 +16374,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16577,7 +16580,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16658,7 +16661,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ76">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR76">
         <v>1.06</v>
@@ -16989,7 +16992,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17195,7 +17198,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17273,7 +17276,7 @@
         <v>1</v>
       </c>
       <c r="AP79">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17401,7 +17404,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17688,7 +17691,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ81">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR81">
         <v>1.51</v>
@@ -17813,7 +17816,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18019,7 +18022,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18431,7 +18434,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18843,7 +18846,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19461,7 +19464,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19667,7 +19670,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19873,7 +19876,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20160,7 +20163,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ93">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR93">
         <v>1.95</v>
@@ -20285,7 +20288,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20491,7 +20494,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20697,7 +20700,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -21109,7 +21112,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21315,7 +21318,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21393,7 +21396,7 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
         <v>0.89</v>
@@ -21933,7 +21936,7 @@
         <v>150</v>
       </c>
       <c r="P102" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -22345,7 +22348,7 @@
         <v>84</v>
       </c>
       <c r="P104" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q104">
         <v>7.5</v>
@@ -22835,7 +22838,7 @@
         <v>1.86</v>
       </c>
       <c r="AP106">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ106">
         <v>1.89</v>
@@ -23787,7 +23790,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -23993,7 +23996,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24280,7 +24283,7 @@
         <v>1</v>
       </c>
       <c r="AQ113">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR113">
         <v>1.13</v>
@@ -24483,7 +24486,7 @@
         <v>0.75</v>
       </c>
       <c r="AP114">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ114">
         <v>0.67</v>
@@ -24817,7 +24820,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25023,7 +25026,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25229,7 +25232,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25435,7 +25438,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25641,7 +25644,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -26053,7 +26056,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26259,7 +26262,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26465,7 +26468,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26546,7 +26549,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ124">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR124">
         <v>1.66</v>
@@ -27240,6 +27243,212 @@
       </c>
       <c r="BP127">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7537417</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F128">
+        <v>19</v>
+      </c>
+      <c r="G128" t="s">
+        <v>83</v>
+      </c>
+      <c r="H128" t="s">
+        <v>70</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>2</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>2</v>
+      </c>
+      <c r="O128" t="s">
+        <v>166</v>
+      </c>
+      <c r="P128" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q128">
+        <v>3.1</v>
+      </c>
+      <c r="R128">
+        <v>1.95</v>
+      </c>
+      <c r="S128">
+        <v>4</v>
+      </c>
+      <c r="T128">
+        <v>1.53</v>
+      </c>
+      <c r="U128">
+        <v>2.38</v>
+      </c>
+      <c r="V128">
+        <v>3.75</v>
+      </c>
+      <c r="W128">
+        <v>1.25</v>
+      </c>
+      <c r="X128">
+        <v>11</v>
+      </c>
+      <c r="Y128">
+        <v>1.05</v>
+      </c>
+      <c r="Z128">
+        <v>2.4</v>
+      </c>
+      <c r="AA128">
+        <v>3.05</v>
+      </c>
+      <c r="AB128">
+        <v>3.25</v>
+      </c>
+      <c r="AC128">
+        <v>1.1</v>
+      </c>
+      <c r="AD128">
+        <v>4.6</v>
+      </c>
+      <c r="AE128">
+        <v>1.46</v>
+      </c>
+      <c r="AF128">
+        <v>2.55</v>
+      </c>
+      <c r="AG128">
+        <v>1.97</v>
+      </c>
+      <c r="AH128">
+        <v>1.74</v>
+      </c>
+      <c r="AI128">
+        <v>2</v>
+      </c>
+      <c r="AJ128">
+        <v>1.75</v>
+      </c>
+      <c r="AK128">
+        <v>1.34</v>
+      </c>
+      <c r="AL128">
+        <v>1.4</v>
+      </c>
+      <c r="AM128">
+        <v>1.6</v>
+      </c>
+      <c r="AN128">
+        <v>0.78</v>
+      </c>
+      <c r="AO128">
+        <v>1.67</v>
+      </c>
+      <c r="AP128">
+        <v>1</v>
+      </c>
+      <c r="AQ128">
+        <v>1.5</v>
+      </c>
+      <c r="AR128">
+        <v>1.37</v>
+      </c>
+      <c r="AS128">
+        <v>0.93</v>
+      </c>
+      <c r="AT128">
+        <v>2.3</v>
+      </c>
+      <c r="AU128">
+        <v>5</v>
+      </c>
+      <c r="AV128">
+        <v>3</v>
+      </c>
+      <c r="AW128">
+        <v>6</v>
+      </c>
+      <c r="AX128">
+        <v>8</v>
+      </c>
+      <c r="AY128">
+        <v>13</v>
+      </c>
+      <c r="AZ128">
+        <v>14</v>
+      </c>
+      <c r="BA128">
+        <v>3</v>
+      </c>
+      <c r="BB128">
+        <v>3</v>
+      </c>
+      <c r="BC128">
+        <v>6</v>
+      </c>
+      <c r="BD128">
+        <v>1.79</v>
+      </c>
+      <c r="BE128">
+        <v>6.4</v>
+      </c>
+      <c r="BF128">
+        <v>2.25</v>
+      </c>
+      <c r="BG128">
+        <v>1.41</v>
+      </c>
+      <c r="BH128">
+        <v>2.48</v>
+      </c>
+      <c r="BI128">
+        <v>1.71</v>
+      </c>
+      <c r="BJ128">
+        <v>1.9</v>
+      </c>
+      <c r="BK128">
+        <v>2.15</v>
+      </c>
+      <c r="BL128">
+        <v>1.55</v>
+      </c>
+      <c r="BM128">
+        <v>2.8</v>
+      </c>
+      <c r="BN128">
+        <v>1.32</v>
+      </c>
+      <c r="BO128">
+        <v>3.75</v>
+      </c>
+      <c r="BP128">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="238">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -517,6 +517,9 @@
     <t>['73', '90+4']</t>
   </si>
   <si>
+    <t>['38']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -719,6 +722,12 @@
   </si>
   <si>
     <t>['90+2', '90+4']</t>
+  </si>
+  <si>
+    <t>['18', '23']</t>
+  </si>
+  <si>
+    <t>['76', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP128"/>
+  <dimension ref="A1:BP133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1336,7 +1345,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1417,7 +1426,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ2">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1542,7 +1551,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -1826,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
         <v>0.5600000000000001</v>
@@ -2032,10 +2041,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ5">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2160,7 +2169,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2238,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ6">
         <v>0.89</v>
@@ -2447,7 +2456,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ7">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2572,7 +2581,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2650,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ8">
         <v>0.67</v>
@@ -2984,7 +2993,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3190,7 +3199,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3396,7 +3405,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3886,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ14">
         <v>0.89</v>
@@ -4014,7 +4023,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q15">
         <v>1.44</v>
@@ -4220,7 +4229,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4301,7 +4310,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ16">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4426,7 +4435,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4504,10 +4513,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4710,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -4838,7 +4847,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -4916,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR19">
         <v>1.38</v>
@@ -5044,7 +5053,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5125,7 +5134,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ20">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR20">
         <v>0.67</v>
@@ -5250,7 +5259,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5328,10 +5337,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ21">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR21">
         <v>1.23</v>
@@ -5456,7 +5465,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5868,7 +5877,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6074,7 +6083,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6692,7 +6701,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7104,7 +7113,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7185,7 +7194,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ30">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR30">
         <v>0.96</v>
@@ -7388,10 +7397,10 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR31">
         <v>1.29</v>
@@ -7516,7 +7525,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7594,10 +7603,10 @@
         <v>2</v>
       </c>
       <c r="AP32">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ32">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR32">
         <v>1.34</v>
@@ -7800,10 +7809,10 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ33">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR33">
         <v>0.97</v>
@@ -7928,7 +7937,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8006,7 +8015,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8134,7 +8143,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8212,7 +8221,7 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ35">
         <v>0.67</v>
@@ -8421,7 +8430,7 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR36">
         <v>2.14</v>
@@ -8546,7 +8555,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8752,7 +8761,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -8958,7 +8967,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9782,7 +9791,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9988,7 +9997,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10066,7 +10075,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ44">
         <v>1.5</v>
@@ -10272,10 +10281,10 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ45">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR45">
         <v>1.33</v>
@@ -10478,7 +10487,7 @@
         <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>0.67</v>
@@ -10606,7 +10615,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10687,7 +10696,7 @@
         <v>1</v>
       </c>
       <c r="AQ47">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR47">
         <v>1.06</v>
@@ -10812,7 +10821,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10893,7 +10902,7 @@
         <v>1</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR48">
         <v>1.58</v>
@@ -11018,7 +11027,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11096,10 +11105,10 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ49">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR49">
         <v>1.09</v>
@@ -11302,10 +11311,10 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ50">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR50">
         <v>1.74</v>
@@ -11636,7 +11645,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -11714,7 +11723,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ52">
         <v>1.44</v>
@@ -11923,7 +11932,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR53">
         <v>1.1</v>
@@ -12048,7 +12057,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12254,7 +12263,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12538,7 +12547,7 @@
         <v>0.75</v>
       </c>
       <c r="AP56">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
         <v>0.5600000000000001</v>
@@ -12666,7 +12675,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12747,7 +12756,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ57">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR57">
         <v>1.84</v>
@@ -12872,7 +12881,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -12950,7 +12959,7 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ58">
         <v>1.5</v>
@@ -13078,7 +13087,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13156,7 +13165,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ59">
         <v>0.67</v>
@@ -13365,7 +13374,7 @@
         <v>1</v>
       </c>
       <c r="AQ60">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR60">
         <v>1.32</v>
@@ -13571,7 +13580,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ61">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR61">
         <v>1.69</v>
@@ -13696,7 +13705,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13774,7 +13783,7 @@
         <v>1.75</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ62">
         <v>0.89</v>
@@ -13902,7 +13911,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -13983,7 +13992,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ63">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
         <v>1.69</v>
@@ -14108,7 +14117,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14726,7 +14735,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -14804,7 +14813,7 @@
         <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
         <v>0.89</v>
@@ -14932,7 +14941,7 @@
         <v>84</v>
       </c>
       <c r="P68" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q68">
         <v>6.5</v>
@@ -15138,7 +15147,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15216,10 +15225,10 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ69">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR69">
         <v>1.44</v>
@@ -15344,7 +15353,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15425,7 +15434,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ70">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR70">
         <v>1.11</v>
@@ -15631,7 +15640,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ71">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR71">
         <v>1.51</v>
@@ -15834,7 +15843,7 @@
         <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ72">
         <v>0.89</v>
@@ -15962,7 +15971,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16249,7 +16258,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ74">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR74">
         <v>1.64</v>
@@ -16374,7 +16383,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16580,7 +16589,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16658,7 +16667,7 @@
         <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
         <v>1.5</v>
@@ -16864,7 +16873,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ77">
         <v>0.67</v>
@@ -16992,7 +17001,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17073,7 +17082,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ78">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR78">
         <v>1.72</v>
@@ -17198,7 +17207,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17404,7 +17413,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17485,7 +17494,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ80">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR80">
         <v>1.08</v>
@@ -17688,7 +17697,7 @@
         <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
         <v>1.5</v>
@@ -17816,7 +17825,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -17894,7 +17903,7 @@
         <v>1.6</v>
       </c>
       <c r="AP82">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ82">
         <v>2</v>
@@ -18022,7 +18031,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18103,7 +18112,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ83">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR83">
         <v>1.54</v>
@@ -18309,7 +18318,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ84">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR84">
         <v>2.03</v>
@@ -18434,7 +18443,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18512,7 +18521,7 @@
         <v>0.6</v>
       </c>
       <c r="AP85">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ85">
         <v>0.89</v>
@@ -18846,7 +18855,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -18924,7 +18933,7 @@
         <v>1.6</v>
       </c>
       <c r="AP87">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ87">
         <v>1.44</v>
@@ -19339,7 +19348,7 @@
         <v>1</v>
       </c>
       <c r="AQ89">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR89">
         <v>1.12</v>
@@ -19464,7 +19473,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19545,7 +19554,7 @@
         <v>1</v>
       </c>
       <c r="AQ90">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR90">
         <v>1.22</v>
@@ -19670,7 +19679,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19876,7 +19885,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -19954,7 +19963,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ92">
         <v>1.56</v>
@@ -20288,7 +20297,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20366,7 +20375,7 @@
         <v>1.83</v>
       </c>
       <c r="AP94">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
         <v>1.56</v>
@@ -20494,7 +20503,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20575,7 +20584,7 @@
         <v>1</v>
       </c>
       <c r="AQ95">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR95">
         <v>1.27</v>
@@ -20700,7 +20709,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -20781,7 +20790,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR96">
         <v>1.22</v>
@@ -21112,7 +21121,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21318,7 +21327,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21605,7 +21614,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ100">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR100">
         <v>1.18</v>
@@ -21808,10 +21817,10 @@
         <v>1.57</v>
       </c>
       <c r="AP101">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ101">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR101">
         <v>1.32</v>
@@ -21936,7 +21945,7 @@
         <v>150</v>
       </c>
       <c r="P102" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -22017,7 +22026,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ102">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR102">
         <v>1.38</v>
@@ -22220,7 +22229,7 @@
         <v>1.29</v>
       </c>
       <c r="AP103">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ103">
         <v>1</v>
@@ -22348,7 +22357,7 @@
         <v>84</v>
       </c>
       <c r="P104" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q104">
         <v>7.5</v>
@@ -22426,7 +22435,7 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ104">
         <v>2</v>
@@ -22632,10 +22641,10 @@
         <v>2.71</v>
       </c>
       <c r="AP105">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ105">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR105">
         <v>1.29</v>
@@ -22841,7 +22850,7 @@
         <v>1</v>
       </c>
       <c r="AQ106">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR106">
         <v>1.5</v>
@@ -23456,7 +23465,7 @@
         <v>0.71</v>
       </c>
       <c r="AP109">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ109">
         <v>0.5600000000000001</v>
@@ -23790,7 +23799,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -23996,7 +24005,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24692,7 +24701,7 @@
         <v>1.13</v>
       </c>
       <c r="AP115">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -24820,7 +24829,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -24898,10 +24907,10 @@
         <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR116">
         <v>1.47</v>
@@ -25026,7 +25035,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25107,7 +25116,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ117">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR117">
         <v>1.31</v>
@@ -25232,7 +25241,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25310,10 +25319,10 @@
         <v>1.13</v>
       </c>
       <c r="AP118">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ118">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR118">
         <v>1.32</v>
@@ -25438,7 +25447,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25516,10 +25525,10 @@
         <v>2.75</v>
       </c>
       <c r="AP119">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ119">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR119">
         <v>1.85</v>
@@ -25644,7 +25653,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -25722,10 +25731,10 @@
         <v>1.75</v>
       </c>
       <c r="AP120">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ120">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR120">
         <v>1.23</v>
@@ -26056,7 +26065,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26262,7 +26271,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26468,7 +26477,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -27449,6 +27458,1036 @@
       </c>
       <c r="BP128">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7537419</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45676.41666666666</v>
+      </c>
+      <c r="F129">
+        <v>19</v>
+      </c>
+      <c r="G129" t="s">
+        <v>74</v>
+      </c>
+      <c r="H129" t="s">
+        <v>80</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129">
+        <v>2</v>
+      </c>
+      <c r="K129">
+        <v>3</v>
+      </c>
+      <c r="L129">
+        <v>1</v>
+      </c>
+      <c r="M129">
+        <v>2</v>
+      </c>
+      <c r="N129">
+        <v>3</v>
+      </c>
+      <c r="O129" t="s">
+        <v>108</v>
+      </c>
+      <c r="P129" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q129">
+        <v>7</v>
+      </c>
+      <c r="R129">
+        <v>2.1</v>
+      </c>
+      <c r="S129">
+        <v>2.2</v>
+      </c>
+      <c r="T129">
+        <v>1.44</v>
+      </c>
+      <c r="U129">
+        <v>2.63</v>
+      </c>
+      <c r="V129">
+        <v>3.25</v>
+      </c>
+      <c r="W129">
+        <v>1.33</v>
+      </c>
+      <c r="X129">
+        <v>10</v>
+      </c>
+      <c r="Y129">
+        <v>1.06</v>
+      </c>
+      <c r="Z129">
+        <v>6.71</v>
+      </c>
+      <c r="AA129">
+        <v>4.15</v>
+      </c>
+      <c r="AB129">
+        <v>1.46</v>
+      </c>
+      <c r="AC129">
+        <v>1.07</v>
+      </c>
+      <c r="AD129">
+        <v>5.4</v>
+      </c>
+      <c r="AE129">
+        <v>1.39</v>
+      </c>
+      <c r="AF129">
+        <v>2.85</v>
+      </c>
+      <c r="AG129">
+        <v>2.09</v>
+      </c>
+      <c r="AH129">
+        <v>1.66</v>
+      </c>
+      <c r="AI129">
+        <v>2.2</v>
+      </c>
+      <c r="AJ129">
+        <v>1.62</v>
+      </c>
+      <c r="AK129">
+        <v>2.44</v>
+      </c>
+      <c r="AL129">
+        <v>1.27</v>
+      </c>
+      <c r="AM129">
+        <v>1.12</v>
+      </c>
+      <c r="AN129">
+        <v>0.89</v>
+      </c>
+      <c r="AO129">
+        <v>1.89</v>
+      </c>
+      <c r="AP129">
+        <v>0.8</v>
+      </c>
+      <c r="AQ129">
+        <v>2</v>
+      </c>
+      <c r="AR129">
+        <v>1.26</v>
+      </c>
+      <c r="AS129">
+        <v>1.79</v>
+      </c>
+      <c r="AT129">
+        <v>3.05</v>
+      </c>
+      <c r="AU129">
+        <v>2</v>
+      </c>
+      <c r="AV129">
+        <v>10</v>
+      </c>
+      <c r="AW129">
+        <v>2</v>
+      </c>
+      <c r="AX129">
+        <v>9</v>
+      </c>
+      <c r="AY129">
+        <v>4</v>
+      </c>
+      <c r="AZ129">
+        <v>19</v>
+      </c>
+      <c r="BA129">
+        <v>3</v>
+      </c>
+      <c r="BB129">
+        <v>5</v>
+      </c>
+      <c r="BC129">
+        <v>8</v>
+      </c>
+      <c r="BD129">
+        <v>3.15</v>
+      </c>
+      <c r="BE129">
+        <v>6.75</v>
+      </c>
+      <c r="BF129">
+        <v>1.45</v>
+      </c>
+      <c r="BG129">
+        <v>1.44</v>
+      </c>
+      <c r="BH129">
+        <v>2.4</v>
+      </c>
+      <c r="BI129">
+        <v>1.75</v>
+      </c>
+      <c r="BJ129">
+        <v>1.86</v>
+      </c>
+      <c r="BK129">
+        <v>2.2</v>
+      </c>
+      <c r="BL129">
+        <v>1.52</v>
+      </c>
+      <c r="BM129">
+        <v>2.88</v>
+      </c>
+      <c r="BN129">
+        <v>1.3</v>
+      </c>
+      <c r="BO129">
+        <v>3.85</v>
+      </c>
+      <c r="BP129">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7537420</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45676.47916666666</v>
+      </c>
+      <c r="F130">
+        <v>19</v>
+      </c>
+      <c r="G130" t="s">
+        <v>72</v>
+      </c>
+      <c r="H130" t="s">
+        <v>79</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>1</v>
+      </c>
+      <c r="M130">
+        <v>2</v>
+      </c>
+      <c r="N130">
+        <v>3</v>
+      </c>
+      <c r="O130" t="s">
+        <v>104</v>
+      </c>
+      <c r="P130" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q130">
+        <v>3.25</v>
+      </c>
+      <c r="R130">
+        <v>1.91</v>
+      </c>
+      <c r="S130">
+        <v>4</v>
+      </c>
+      <c r="T130">
+        <v>1.57</v>
+      </c>
+      <c r="U130">
+        <v>2.25</v>
+      </c>
+      <c r="V130">
+        <v>3.75</v>
+      </c>
+      <c r="W130">
+        <v>1.25</v>
+      </c>
+      <c r="X130">
+        <v>13</v>
+      </c>
+      <c r="Y130">
+        <v>1.04</v>
+      </c>
+      <c r="Z130">
+        <v>2.45</v>
+      </c>
+      <c r="AA130">
+        <v>2.9</v>
+      </c>
+      <c r="AB130">
+        <v>3</v>
+      </c>
+      <c r="AC130">
+        <v>1.11</v>
+      </c>
+      <c r="AD130">
+        <v>4.3</v>
+      </c>
+      <c r="AE130">
+        <v>1.5</v>
+      </c>
+      <c r="AF130">
+        <v>2.4</v>
+      </c>
+      <c r="AG130">
+        <v>2.1</v>
+      </c>
+      <c r="AH130">
+        <v>1.6</v>
+      </c>
+      <c r="AI130">
+        <v>2.05</v>
+      </c>
+      <c r="AJ130">
+        <v>1.7</v>
+      </c>
+      <c r="AK130">
+        <v>1.36</v>
+      </c>
+      <c r="AL130">
+        <v>1.42</v>
+      </c>
+      <c r="AM130">
+        <v>1.54</v>
+      </c>
+      <c r="AN130">
+        <v>1.11</v>
+      </c>
+      <c r="AO130">
+        <v>1.33</v>
+      </c>
+      <c r="AP130">
+        <v>1</v>
+      </c>
+      <c r="AQ130">
+        <v>1.5</v>
+      </c>
+      <c r="AR130">
+        <v>1.17</v>
+      </c>
+      <c r="AS130">
+        <v>1.09</v>
+      </c>
+      <c r="AT130">
+        <v>2.26</v>
+      </c>
+      <c r="AU130">
+        <v>5</v>
+      </c>
+      <c r="AV130">
+        <v>5</v>
+      </c>
+      <c r="AW130">
+        <v>2</v>
+      </c>
+      <c r="AX130">
+        <v>7</v>
+      </c>
+      <c r="AY130">
+        <v>8</v>
+      </c>
+      <c r="AZ130">
+        <v>15</v>
+      </c>
+      <c r="BA130">
+        <v>2</v>
+      </c>
+      <c r="BB130">
+        <v>5</v>
+      </c>
+      <c r="BC130">
+        <v>7</v>
+      </c>
+      <c r="BD130">
+        <v>1.89</v>
+      </c>
+      <c r="BE130">
+        <v>6.25</v>
+      </c>
+      <c r="BF130">
+        <v>2.15</v>
+      </c>
+      <c r="BG130">
+        <v>1.49</v>
+      </c>
+      <c r="BH130">
+        <v>2.28</v>
+      </c>
+      <c r="BI130">
+        <v>1.84</v>
+      </c>
+      <c r="BJ130">
+        <v>1.76</v>
+      </c>
+      <c r="BK130">
+        <v>2.35</v>
+      </c>
+      <c r="BL130">
+        <v>1.46</v>
+      </c>
+      <c r="BM130">
+        <v>3.15</v>
+      </c>
+      <c r="BN130">
+        <v>1.26</v>
+      </c>
+      <c r="BO130">
+        <v>4.25</v>
+      </c>
+      <c r="BP130">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7537422</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45676.47916666666</v>
+      </c>
+      <c r="F131">
+        <v>19</v>
+      </c>
+      <c r="G131" t="s">
+        <v>76</v>
+      </c>
+      <c r="H131" t="s">
+        <v>77</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>1</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>1</v>
+      </c>
+      <c r="O131" t="s">
+        <v>120</v>
+      </c>
+      <c r="P131" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q131">
+        <v>3.1</v>
+      </c>
+      <c r="R131">
+        <v>2</v>
+      </c>
+      <c r="S131">
+        <v>3.75</v>
+      </c>
+      <c r="T131">
+        <v>1.5</v>
+      </c>
+      <c r="U131">
+        <v>2.5</v>
+      </c>
+      <c r="V131">
+        <v>3.4</v>
+      </c>
+      <c r="W131">
+        <v>1.3</v>
+      </c>
+      <c r="X131">
+        <v>10</v>
+      </c>
+      <c r="Y131">
+        <v>1.06</v>
+      </c>
+      <c r="Z131">
+        <v>2.4</v>
+      </c>
+      <c r="AA131">
+        <v>3.1</v>
+      </c>
+      <c r="AB131">
+        <v>2.9</v>
+      </c>
+      <c r="AC131">
+        <v>1.09</v>
+      </c>
+      <c r="AD131">
+        <v>5</v>
+      </c>
+      <c r="AE131">
+        <v>1.41</v>
+      </c>
+      <c r="AF131">
+        <v>2.75</v>
+      </c>
+      <c r="AG131">
+        <v>2.15</v>
+      </c>
+      <c r="AH131">
+        <v>1.57</v>
+      </c>
+      <c r="AI131">
+        <v>1.95</v>
+      </c>
+      <c r="AJ131">
+        <v>1.8</v>
+      </c>
+      <c r="AK131">
+        <v>1.39</v>
+      </c>
+      <c r="AL131">
+        <v>1.39</v>
+      </c>
+      <c r="AM131">
+        <v>1.54</v>
+      </c>
+      <c r="AN131">
+        <v>1.11</v>
+      </c>
+      <c r="AO131">
+        <v>1.67</v>
+      </c>
+      <c r="AP131">
+        <v>1.3</v>
+      </c>
+      <c r="AQ131">
+        <v>1.5</v>
+      </c>
+      <c r="AR131">
+        <v>1.17</v>
+      </c>
+      <c r="AS131">
+        <v>1</v>
+      </c>
+      <c r="AT131">
+        <v>2.17</v>
+      </c>
+      <c r="AU131">
+        <v>5</v>
+      </c>
+      <c r="AV131">
+        <v>4</v>
+      </c>
+      <c r="AW131">
+        <v>5</v>
+      </c>
+      <c r="AX131">
+        <v>6</v>
+      </c>
+      <c r="AY131">
+        <v>11</v>
+      </c>
+      <c r="AZ131">
+        <v>12</v>
+      </c>
+      <c r="BA131">
+        <v>4</v>
+      </c>
+      <c r="BB131">
+        <v>4</v>
+      </c>
+      <c r="BC131">
+        <v>8</v>
+      </c>
+      <c r="BD131">
+        <v>1.95</v>
+      </c>
+      <c r="BE131">
+        <v>5.55</v>
+      </c>
+      <c r="BF131">
+        <v>2.3</v>
+      </c>
+      <c r="BG131">
+        <v>1.51</v>
+      </c>
+      <c r="BH131">
+        <v>2.32</v>
+      </c>
+      <c r="BI131">
+        <v>1.98</v>
+      </c>
+      <c r="BJ131">
+        <v>1.82</v>
+      </c>
+      <c r="BK131">
+        <v>2.54</v>
+      </c>
+      <c r="BL131">
+        <v>1.43</v>
+      </c>
+      <c r="BM131">
+        <v>3.5</v>
+      </c>
+      <c r="BN131">
+        <v>1.22</v>
+      </c>
+      <c r="BO131">
+        <v>4.75</v>
+      </c>
+      <c r="BP131">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7537418</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45676.58333333334</v>
+      </c>
+      <c r="F132">
+        <v>19</v>
+      </c>
+      <c r="G132" t="s">
+        <v>82</v>
+      </c>
+      <c r="H132" t="s">
+        <v>71</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132" t="s">
+        <v>84</v>
+      </c>
+      <c r="P132" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q132">
+        <v>4.33</v>
+      </c>
+      <c r="R132">
+        <v>2.05</v>
+      </c>
+      <c r="S132">
+        <v>2.88</v>
+      </c>
+      <c r="T132">
+        <v>1.5</v>
+      </c>
+      <c r="U132">
+        <v>2.5</v>
+      </c>
+      <c r="V132">
+        <v>3.4</v>
+      </c>
+      <c r="W132">
+        <v>1.3</v>
+      </c>
+      <c r="X132">
+        <v>10</v>
+      </c>
+      <c r="Y132">
+        <v>1.06</v>
+      </c>
+      <c r="Z132">
+        <v>3.41</v>
+      </c>
+      <c r="AA132">
+        <v>3.32</v>
+      </c>
+      <c r="AB132">
+        <v>2.07</v>
+      </c>
+      <c r="AC132">
+        <v>1.08</v>
+      </c>
+      <c r="AD132">
+        <v>5.2</v>
+      </c>
+      <c r="AE132">
+        <v>1.38</v>
+      </c>
+      <c r="AF132">
+        <v>2.9</v>
+      </c>
+      <c r="AG132">
+        <v>2.15</v>
+      </c>
+      <c r="AH132">
+        <v>1.67</v>
+      </c>
+      <c r="AI132">
+        <v>1.95</v>
+      </c>
+      <c r="AJ132">
+        <v>1.8</v>
+      </c>
+      <c r="AK132">
+        <v>1.71</v>
+      </c>
+      <c r="AL132">
+        <v>1.37</v>
+      </c>
+      <c r="AM132">
+        <v>1.29</v>
+      </c>
+      <c r="AN132">
+        <v>2.11</v>
+      </c>
+      <c r="AO132">
+        <v>2.44</v>
+      </c>
+      <c r="AP132">
+        <v>2</v>
+      </c>
+      <c r="AQ132">
+        <v>2.3</v>
+      </c>
+      <c r="AR132">
+        <v>1.43</v>
+      </c>
+      <c r="AS132">
+        <v>1.54</v>
+      </c>
+      <c r="AT132">
+        <v>2.97</v>
+      </c>
+      <c r="AU132">
+        <v>4</v>
+      </c>
+      <c r="AV132">
+        <v>6</v>
+      </c>
+      <c r="AW132">
+        <v>9</v>
+      </c>
+      <c r="AX132">
+        <v>11</v>
+      </c>
+      <c r="AY132">
+        <v>17</v>
+      </c>
+      <c r="AZ132">
+        <v>21</v>
+      </c>
+      <c r="BA132">
+        <v>5</v>
+      </c>
+      <c r="BB132">
+        <v>3</v>
+      </c>
+      <c r="BC132">
+        <v>8</v>
+      </c>
+      <c r="BD132">
+        <v>2.33</v>
+      </c>
+      <c r="BE132">
+        <v>6.1</v>
+      </c>
+      <c r="BF132">
+        <v>1.76</v>
+      </c>
+      <c r="BG132">
+        <v>1.42</v>
+      </c>
+      <c r="BH132">
+        <v>2.45</v>
+      </c>
+      <c r="BI132">
+        <v>1.73</v>
+      </c>
+      <c r="BJ132">
+        <v>1.88</v>
+      </c>
+      <c r="BK132">
+        <v>2.18</v>
+      </c>
+      <c r="BL132">
+        <v>1.53</v>
+      </c>
+      <c r="BM132">
+        <v>2.85</v>
+      </c>
+      <c r="BN132">
+        <v>1.32</v>
+      </c>
+      <c r="BO132">
+        <v>3.8</v>
+      </c>
+      <c r="BP132">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7537421</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45676.64583333334</v>
+      </c>
+      <c r="F133">
+        <v>19</v>
+      </c>
+      <c r="G133" t="s">
+        <v>73</v>
+      </c>
+      <c r="H133" t="s">
+        <v>75</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>1</v>
+      </c>
+      <c r="O133" t="s">
+        <v>167</v>
+      </c>
+      <c r="P133" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q133">
+        <v>3.4</v>
+      </c>
+      <c r="R133">
+        <v>2.05</v>
+      </c>
+      <c r="S133">
+        <v>3.4</v>
+      </c>
+      <c r="T133">
+        <v>1.44</v>
+      </c>
+      <c r="U133">
+        <v>2.63</v>
+      </c>
+      <c r="V133">
+        <v>3.4</v>
+      </c>
+      <c r="W133">
+        <v>1.3</v>
+      </c>
+      <c r="X133">
+        <v>10</v>
+      </c>
+      <c r="Y133">
+        <v>1.06</v>
+      </c>
+      <c r="Z133">
+        <v>2.5</v>
+      </c>
+      <c r="AA133">
+        <v>3.2</v>
+      </c>
+      <c r="AB133">
+        <v>2.7</v>
+      </c>
+      <c r="AC133">
+        <v>1.08</v>
+      </c>
+      <c r="AD133">
+        <v>5.2</v>
+      </c>
+      <c r="AE133">
+        <v>1.39</v>
+      </c>
+      <c r="AF133">
+        <v>2.85</v>
+      </c>
+      <c r="AG133">
+        <v>2.05</v>
+      </c>
+      <c r="AH133">
+        <v>1.65</v>
+      </c>
+      <c r="AI133">
+        <v>1.91</v>
+      </c>
+      <c r="AJ133">
+        <v>1.91</v>
+      </c>
+      <c r="AK133">
+        <v>1.47</v>
+      </c>
+      <c r="AL133">
+        <v>1.37</v>
+      </c>
+      <c r="AM133">
+        <v>1.48</v>
+      </c>
+      <c r="AN133">
+        <v>2</v>
+      </c>
+      <c r="AO133">
+        <v>1.78</v>
+      </c>
+      <c r="AP133">
+        <v>2.1</v>
+      </c>
+      <c r="AQ133">
+        <v>1.6</v>
+      </c>
+      <c r="AR133">
+        <v>1.91</v>
+      </c>
+      <c r="AS133">
+        <v>1.76</v>
+      </c>
+      <c r="AT133">
+        <v>3.67</v>
+      </c>
+      <c r="AU133">
+        <v>4</v>
+      </c>
+      <c r="AV133">
+        <v>3</v>
+      </c>
+      <c r="AW133">
+        <v>4</v>
+      </c>
+      <c r="AX133">
+        <v>7</v>
+      </c>
+      <c r="AY133">
+        <v>8</v>
+      </c>
+      <c r="AZ133">
+        <v>14</v>
+      </c>
+      <c r="BA133">
+        <v>0</v>
+      </c>
+      <c r="BB133">
+        <v>7</v>
+      </c>
+      <c r="BC133">
+        <v>7</v>
+      </c>
+      <c r="BD133">
+        <v>1.86</v>
+      </c>
+      <c r="BE133">
+        <v>6.75</v>
+      </c>
+      <c r="BF133">
+        <v>2.12</v>
+      </c>
+      <c r="BG133">
+        <v>1.21</v>
+      </c>
+      <c r="BH133">
+        <v>3.5</v>
+      </c>
+      <c r="BI133">
+        <v>1.38</v>
+      </c>
+      <c r="BJ133">
+        <v>2.6</v>
+      </c>
+      <c r="BK133">
+        <v>1.64</v>
+      </c>
+      <c r="BL133">
+        <v>2</v>
+      </c>
+      <c r="BM133">
+        <v>2.02</v>
+      </c>
+      <c r="BN133">
+        <v>1.62</v>
+      </c>
+      <c r="BO133">
+        <v>2.6</v>
+      </c>
+      <c r="BP133">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="239">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -518,6 +518,9 @@
   </si>
   <si>
     <t>['38']</t>
+  </si>
+  <si>
+    <t>['22', '61']</t>
   </si>
   <si>
     <t>['13', '73']</t>
@@ -1089,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP133"/>
+  <dimension ref="A1:BP134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1345,7 +1348,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1551,7 +1554,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -2169,7 +2172,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2581,7 +2584,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2662,7 +2665,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ8">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2993,7 +2996,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3071,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ10">
         <v>0.89</v>
@@ -3199,7 +3202,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3280,7 +3283,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ11">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR11">
         <v>2.01</v>
@@ -3405,7 +3408,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -4023,7 +4026,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q15">
         <v>1.44</v>
@@ -4229,7 +4232,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4435,7 +4438,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4847,7 +4850,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5053,7 +5056,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5259,7 +5262,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5465,7 +5468,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5877,7 +5880,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6083,7 +6086,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6161,7 +6164,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ25">
         <v>0.89</v>
@@ -6701,7 +6704,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7113,7 +7116,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7525,7 +7528,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7937,7 +7940,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8143,7 +8146,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8224,7 +8227,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ35">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR35">
         <v>1.08</v>
@@ -8555,7 +8558,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8761,7 +8764,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -8967,7 +8970,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9791,7 +9794,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9997,7 +10000,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10490,7 +10493,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR46">
         <v>1.16</v>
@@ -10615,7 +10618,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10693,7 +10696,7 @@
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ47">
         <v>1.5</v>
@@ -10821,7 +10824,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11027,7 +11030,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11645,7 +11648,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12057,7 +12060,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12263,7 +12266,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12675,7 +12678,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12881,7 +12884,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13087,7 +13090,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13168,7 +13171,7 @@
         <v>1</v>
       </c>
       <c r="AQ59">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR59">
         <v>0.99</v>
@@ -13371,7 +13374,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ60">
         <v>1.6</v>
@@ -13705,7 +13708,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13911,7 +13914,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14117,7 +14120,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14735,7 +14738,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -14941,7 +14944,7 @@
         <v>84</v>
       </c>
       <c r="P68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q68">
         <v>6.5</v>
@@ -15147,7 +15150,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15353,7 +15356,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15971,7 +15974,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16049,7 +16052,7 @@
         <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ73">
         <v>1.56</v>
@@ -16383,7 +16386,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16589,7 +16592,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16876,7 +16879,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ77">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR77">
         <v>1.69</v>
@@ -17001,7 +17004,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17207,7 +17210,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17413,7 +17416,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17825,7 +17828,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18031,7 +18034,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18443,7 +18446,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18730,7 +18733,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ86">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR86">
         <v>1.38</v>
@@ -18855,7 +18858,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19345,7 +19348,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ89">
         <v>1.5</v>
@@ -19473,7 +19476,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19679,7 +19682,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19885,7 +19888,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20297,7 +20300,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20503,7 +20506,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20581,7 +20584,7 @@
         <v>2.67</v>
       </c>
       <c r="AP95">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ95">
         <v>2.3</v>
@@ -20709,7 +20712,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -21121,7 +21124,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21327,7 +21330,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21945,7 +21948,7 @@
         <v>150</v>
       </c>
       <c r="P102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -22357,7 +22360,7 @@
         <v>84</v>
       </c>
       <c r="P104" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q104">
         <v>7.5</v>
@@ -23056,7 +23059,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ107">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR107">
         <v>1.96</v>
@@ -23259,7 +23262,7 @@
         <v>1.71</v>
       </c>
       <c r="AP108">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ108">
         <v>1.44</v>
@@ -23799,7 +23802,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -24005,7 +24008,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24498,7 +24501,7 @@
         <v>1</v>
       </c>
       <c r="AQ114">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR114">
         <v>1.39</v>
@@ -24829,7 +24832,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25035,7 +25038,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25241,7 +25244,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25447,7 +25450,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25653,7 +25656,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -26065,7 +26068,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26143,7 +26146,7 @@
         <v>2.13</v>
       </c>
       <c r="AP122">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ122">
         <v>2</v>
@@ -26271,7 +26274,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26477,7 +26480,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -27507,7 +27510,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27713,7 +27716,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28488,6 +28491,212 @@
       </c>
       <c r="BP133">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7537423</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45677.54166666666</v>
+      </c>
+      <c r="F134">
+        <v>19</v>
+      </c>
+      <c r="G134" t="s">
+        <v>78</v>
+      </c>
+      <c r="H134" t="s">
+        <v>81</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>1</v>
+      </c>
+      <c r="L134">
+        <v>2</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>2</v>
+      </c>
+      <c r="O134" t="s">
+        <v>168</v>
+      </c>
+      <c r="P134" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q134">
+        <v>2.75</v>
+      </c>
+      <c r="R134">
+        <v>2</v>
+      </c>
+      <c r="S134">
+        <v>4.75</v>
+      </c>
+      <c r="T134">
+        <v>1.53</v>
+      </c>
+      <c r="U134">
+        <v>2.38</v>
+      </c>
+      <c r="V134">
+        <v>3.5</v>
+      </c>
+      <c r="W134">
+        <v>1.29</v>
+      </c>
+      <c r="X134">
+        <v>11</v>
+      </c>
+      <c r="Y134">
+        <v>1.05</v>
+      </c>
+      <c r="Z134">
+        <v>1.95</v>
+      </c>
+      <c r="AA134">
+        <v>3.1</v>
+      </c>
+      <c r="AB134">
+        <v>3.9</v>
+      </c>
+      <c r="AC134">
+        <v>1.09</v>
+      </c>
+      <c r="AD134">
+        <v>4.7</v>
+      </c>
+      <c r="AE134">
+        <v>1.45</v>
+      </c>
+      <c r="AF134">
+        <v>2.6</v>
+      </c>
+      <c r="AG134">
+        <v>2.3</v>
+      </c>
+      <c r="AH134">
+        <v>1.55</v>
+      </c>
+      <c r="AI134">
+        <v>2.05</v>
+      </c>
+      <c r="AJ134">
+        <v>1.7</v>
+      </c>
+      <c r="AK134">
+        <v>1.25</v>
+      </c>
+      <c r="AL134">
+        <v>1.36</v>
+      </c>
+      <c r="AM134">
+        <v>1.81</v>
+      </c>
+      <c r="AN134">
+        <v>1</v>
+      </c>
+      <c r="AO134">
+        <v>0.67</v>
+      </c>
+      <c r="AP134">
+        <v>1.2</v>
+      </c>
+      <c r="AQ134">
+        <v>0.6</v>
+      </c>
+      <c r="AR134">
+        <v>1.25</v>
+      </c>
+      <c r="AS134">
+        <v>0.97</v>
+      </c>
+      <c r="AT134">
+        <v>2.22</v>
+      </c>
+      <c r="AU134">
+        <v>7</v>
+      </c>
+      <c r="AV134">
+        <v>2</v>
+      </c>
+      <c r="AW134">
+        <v>13</v>
+      </c>
+      <c r="AX134">
+        <v>7</v>
+      </c>
+      <c r="AY134">
+        <v>20</v>
+      </c>
+      <c r="AZ134">
+        <v>12</v>
+      </c>
+      <c r="BA134">
+        <v>4</v>
+      </c>
+      <c r="BB134">
+        <v>3</v>
+      </c>
+      <c r="BC134">
+        <v>7</v>
+      </c>
+      <c r="BD134">
+        <v>1.46</v>
+      </c>
+      <c r="BE134">
+        <v>6.9</v>
+      </c>
+      <c r="BF134">
+        <v>3.35</v>
+      </c>
+      <c r="BG134">
+        <v>1.56</v>
+      </c>
+      <c r="BH134">
+        <v>2.21</v>
+      </c>
+      <c r="BI134">
+        <v>2.02</v>
+      </c>
+      <c r="BJ134">
+        <v>1.71</v>
+      </c>
+      <c r="BK134">
+        <v>2.67</v>
+      </c>
+      <c r="BL134">
+        <v>1.39</v>
+      </c>
+      <c r="BM134">
+        <v>3.76</v>
+      </c>
+      <c r="BN134">
+        <v>1.19</v>
+      </c>
+      <c r="BO134">
+        <v>4.75</v>
+      </c>
+      <c r="BP134">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
@@ -1426,10 +1426,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1632,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1838,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AQ4">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2044,10 +2044,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="AQ6">
-        <v>0.89</v>
+        <v>1.47</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2456,10 +2456,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2662,10 +2662,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AQ8">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2865,22 +2865,22 @@
         <v>0</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AQ9">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AU9">
         <v>3</v>
@@ -3074,19 +3074,19 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AQ10">
-        <v>0.89</v>
+        <v>1.47</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>2.25</v>
       </c>
       <c r="AU10">
         <v>4</v>
@@ -3280,10 +3280,10 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AQ11">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="AR11">
         <v>2.01</v>
@@ -3480,25 +3480,25 @@
         <v>1.7</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AQ12">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3692,19 +3692,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AQ13">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AR13">
         <v>1.83</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AT13">
-        <v>1.83</v>
+        <v>3.09</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3895,22 +3895,22 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP14">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AQ14">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AT14">
-        <v>1.21</v>
+        <v>2.59</v>
       </c>
       <c r="AU14">
         <v>6</v>
@@ -4098,25 +4098,25 @@
         <v>6.5</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO15">
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AQ15">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS15">
         <v>0.36</v>
       </c>
       <c r="AT15">
-        <v>0.36</v>
+        <v>2.07</v>
       </c>
       <c r="AU15">
         <v>6</v>
@@ -4304,25 +4304,25 @@
         <v>1.05</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO16">
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS16">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AT16">
-        <v>1.71</v>
+        <v>2.48</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4510,25 +4510,25 @@
         <v>2.2</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO17">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AQ17">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS17">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AT17">
-        <v>1.15</v>
+        <v>3.02</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4722,19 +4722,19 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR18">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AS18">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AT18">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="AU18">
         <v>8</v>
@@ -4922,25 +4922,25 @@
         <v>1.03</v>
       </c>
       <c r="AN19">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AQ19">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AR19">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT19">
-        <v>1.38</v>
+        <v>3.42</v>
       </c>
       <c r="AU19">
         <v>2</v>
@@ -5128,25 +5128,25 @@
         <v>1.61</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP20">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AQ20">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR20">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AS20">
-        <v>0.53</v>
+        <v>0.76</v>
       </c>
       <c r="AT20">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5337,22 +5337,22 @@
         <v>1</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="AQ21">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AR21">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT21">
-        <v>1.23</v>
+        <v>3.23</v>
       </c>
       <c r="AU21">
         <v>4</v>
@@ -5540,25 +5540,25 @@
         <v>1.05</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AU22">
         <v>9</v>
@@ -5746,25 +5746,25 @@
         <v>1.63</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO23">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP23">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AQ23">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AR23">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="AS23">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="AT23">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -5952,25 +5952,25 @@
         <v>1.85</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP24">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AQ24">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AR24">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="AS24">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AT24">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6161,22 +6161,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP25">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AQ25">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AR25">
-        <v>0.98</v>
+        <v>1.23</v>
       </c>
       <c r="AS25">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AT25">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6367,22 +6367,22 @@
         <v>3</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP26">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AQ26">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AR26">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AS26">
-        <v>0.73</v>
+        <v>1.14</v>
       </c>
       <c r="AT26">
-        <v>2.21</v>
+        <v>2.78</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6573,22 +6573,22 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP27">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AQ27">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR27">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AS27">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="AT27">
-        <v>3.84</v>
+        <v>3.26</v>
       </c>
       <c r="AU27">
         <v>4</v>
@@ -6776,25 +6776,25 @@
         <v>1.38</v>
       </c>
       <c r="AN28">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO28">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AQ28">
-        <v>0.89</v>
+        <v>1.47</v>
       </c>
       <c r="AR28">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="AS28">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AT28">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AU28">
         <v>7</v>
@@ -6982,25 +6982,25 @@
         <v>7.5</v>
       </c>
       <c r="AN29">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AQ29">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR29">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AS29">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AT29">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7188,25 +7188,25 @@
         <v>1.06</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AO30">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP30">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AQ30">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AR30">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="AS30">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="AT30">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AU30">
         <v>9</v>
@@ -7394,25 +7394,25 @@
         <v>1.14</v>
       </c>
       <c r="AN31">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO31">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AQ31">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR31">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AS31">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AT31">
-        <v>3.01</v>
+        <v>3.32</v>
       </c>
       <c r="AU31">
         <v>5</v>
@@ -7600,25 +7600,25 @@
         <v>1.65</v>
       </c>
       <c r="AN32">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AQ32">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR32">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="AT32">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AU32">
         <v>4</v>
@@ -7809,22 +7809,22 @@
         <v>0.5</v>
       </c>
       <c r="AO33">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AQ33">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR33">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="AS33">
-        <v>0.65</v>
+        <v>0.93</v>
       </c>
       <c r="AT33">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AU33">
         <v>5</v>
@@ -8012,25 +8012,25 @@
         <v>4.75</v>
       </c>
       <c r="AN34">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO34">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP34">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR34">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AS34">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AT34">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AU34">
         <v>12</v>
@@ -8218,25 +8218,25 @@
         <v>2.05</v>
       </c>
       <c r="AN35">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO35">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AP35">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="AQ35">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="AR35">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AS35">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="AT35">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8424,25 +8424,25 @@
         <v>1.06</v>
       </c>
       <c r="AN36">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO36">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="AQ36">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AR36">
-        <v>2.14</v>
+        <v>1.16</v>
       </c>
       <c r="AS36">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AT36">
-        <v>3.64</v>
+        <v>3.03</v>
       </c>
       <c r="AU36">
         <v>3</v>
@@ -8630,25 +8630,25 @@
         <v>1.64</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AO37">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP37">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AQ37">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AR37">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AS37">
-        <v>0.83</v>
+        <v>1.13</v>
       </c>
       <c r="AT37">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AU37">
         <v>8</v>
@@ -8836,25 +8836,25 @@
         <v>1.96</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO38">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP38">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AQ38">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AR38">
-        <v>1.97</v>
+        <v>1.42</v>
       </c>
       <c r="AS38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AT38">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="AU38">
         <v>3</v>
@@ -9042,25 +9042,25 @@
         <v>1.87</v>
       </c>
       <c r="AN39">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AO39">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP39">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AQ39">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AR39">
-        <v>1.2</v>
+        <v>0.87</v>
       </c>
       <c r="AS39">
-        <v>0.68</v>
+        <v>1.07</v>
       </c>
       <c r="AT39">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9251,22 +9251,22 @@
         <v>2</v>
       </c>
       <c r="AO40">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP40">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AQ40">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AR40">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="AS40">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AT40">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9454,25 +9454,25 @@
         <v>2.6</v>
       </c>
       <c r="AN41">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AO41">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AP41">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AQ41">
-        <v>0.89</v>
+        <v>1.47</v>
       </c>
       <c r="AR41">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AS41">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AT41">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="AU41">
         <v>4</v>
@@ -9660,25 +9660,25 @@
         <v>1.85</v>
       </c>
       <c r="AN42">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AO42">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AP42">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AQ42">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR42">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS42">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AT42">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9866,25 +9866,25 @@
         <v>1.55</v>
       </c>
       <c r="AN43">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO43">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AP43">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR43">
-        <v>1.06</v>
+        <v>0.91</v>
       </c>
       <c r="AS43">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AT43">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="AU43">
         <v>3</v>
@@ -10075,22 +10075,22 @@
         <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP44">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="AQ44">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR44">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AS44">
-        <v>0.82</v>
+        <v>1.17</v>
       </c>
       <c r="AT44">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="AU44">
         <v>4</v>
@@ -10281,22 +10281,22 @@
         <v>1.33</v>
       </c>
       <c r="AO45">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AQ45">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AR45">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AS45">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AT45">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="AU45">
         <v>6</v>
@@ -10484,25 +10484,25 @@
         <v>2.55</v>
       </c>
       <c r="AN46">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AO46">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AQ46">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="AR46">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AS46">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="AT46">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="AU46">
         <v>5</v>
@@ -10690,25 +10690,25 @@
         <v>1.47</v>
       </c>
       <c r="AN47">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO47">
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AQ47">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR47">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AS47">
-        <v>0.66</v>
+        <v>0.91</v>
       </c>
       <c r="AT47">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -10896,25 +10896,25 @@
         <v>1.39</v>
       </c>
       <c r="AN48">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AO48">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP48">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="AQ48">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR48">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="AS48">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="AT48">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="AU48">
         <v>2</v>
@@ -11105,22 +11105,22 @@
         <v>0.67</v>
       </c>
       <c r="AO49">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AP49">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AQ49">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AR49">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AS49">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AT49">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AU49">
         <v>0</v>
@@ -11308,25 +11308,25 @@
         <v>1.49</v>
       </c>
       <c r="AN50">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AP50">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AQ50">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR50">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AS50">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AT50">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11514,25 +11514,25 @@
         <v>1.6</v>
       </c>
       <c r="AN51">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AO51">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="AP51">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR51">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AS51">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT51">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11720,25 +11720,25 @@
         <v>1.18</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AO52">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AP52">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="AQ52">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AR52">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AS52">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="AT52">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -11926,25 +11926,25 @@
         <v>1.3</v>
       </c>
       <c r="AN53">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AO53">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AP53">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AQ53">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR53">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AS53">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AT53">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12132,25 +12132,25 @@
         <v>3.1</v>
       </c>
       <c r="AN54">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO54">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP54">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AQ54">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AR54">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AS54">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AT54">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="AU54">
         <v>8</v>
@@ -12338,25 +12338,25 @@
         <v>1.16</v>
       </c>
       <c r="AN55">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO55">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="AP55">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AQ55">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR55">
-        <v>1.16</v>
+        <v>0.96</v>
       </c>
       <c r="AS55">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AT55">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12544,25 +12544,25 @@
         <v>2.14</v>
       </c>
       <c r="AN56">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO56">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AP56">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AQ56">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AR56">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AS56">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="AT56">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="AU56">
         <v>11</v>
@@ -12750,25 +12750,25 @@
         <v>1.73</v>
       </c>
       <c r="AN57">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO57">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AP57">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AQ57">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AR57">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AS57">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AT57">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="AU57">
         <v>0</v>
@@ -12959,22 +12959,22 @@
         <v>1.75</v>
       </c>
       <c r="AO58">
-        <v>2</v>
+        <v>0.88</v>
       </c>
       <c r="AP58">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AQ58">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR58">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AS58">
-        <v>0.8100000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="AT58">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13162,25 +13162,25 @@
         <v>1.69</v>
       </c>
       <c r="AN59">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AO59">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP59">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AQ59">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="AR59">
+        <v>0.93</v>
+      </c>
+      <c r="AS59">
         <v>0.99</v>
       </c>
-      <c r="AS59">
-        <v>0.88</v>
-      </c>
       <c r="AT59">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AU59">
         <v>6</v>
@@ -13368,25 +13368,25 @@
         <v>1.08</v>
       </c>
       <c r="AN60">
-        <v>0.33</v>
+        <v>0.88</v>
       </c>
       <c r="AO60">
-        <v>1.33</v>
+        <v>1.88</v>
       </c>
       <c r="AP60">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AQ60">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AR60">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AS60">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AT60">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13574,25 +13574,25 @@
         <v>1.08</v>
       </c>
       <c r="AN61">
-        <v>0.33</v>
+        <v>1.25</v>
       </c>
       <c r="AO61">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AP61">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AQ61">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR61">
-        <v>1.69</v>
+        <v>1.29</v>
       </c>
       <c r="AS61">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AT61">
-        <v>3.31</v>
+        <v>3.09</v>
       </c>
       <c r="AU61">
         <v>4</v>
@@ -13780,25 +13780,25 @@
         <v>1.96</v>
       </c>
       <c r="AN62">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO62">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AP62">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AQ62">
-        <v>0.89</v>
+        <v>1.47</v>
       </c>
       <c r="AR62">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AS62">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT62">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -13986,25 +13986,25 @@
         <v>3.05</v>
       </c>
       <c r="AN63">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO63">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AP63">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR63">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AS63">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="AT63">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14192,25 +14192,25 @@
         <v>1.41</v>
       </c>
       <c r="AN64">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AO64">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP64">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="AQ64">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AR64">
-        <v>1.31</v>
+        <v>0.96</v>
       </c>
       <c r="AS64">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AT64">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="AU64">
         <v>4</v>
@@ -14398,25 +14398,25 @@
         <v>3.8</v>
       </c>
       <c r="AN65">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO65">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AP65">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR65">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AS65">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AT65">
-        <v>3.41</v>
+        <v>3.16</v>
       </c>
       <c r="AU65">
         <v>9</v>
@@ -14604,25 +14604,25 @@
         <v>1.48</v>
       </c>
       <c r="AN66">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO66">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="AQ66">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AR66">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="AS66">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="AT66">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14810,22 +14810,22 @@
         <v>2.2</v>
       </c>
       <c r="AN67">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO67">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AQ67">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AR67">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AS67">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="AT67">
         <v>2.33</v>
@@ -15016,25 +15016,25 @@
         <v>1.12</v>
       </c>
       <c r="AN68">
-        <v>0.2</v>
+        <v>1.11</v>
       </c>
       <c r="AO68">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AP68">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AQ68">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR68">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AS68">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AT68">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15222,25 +15222,25 @@
         <v>1.14</v>
       </c>
       <c r="AN69">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="AO69">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP69">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="AQ69">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AR69">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AS69">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AT69">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15428,25 +15428,25 @@
         <v>1.08</v>
       </c>
       <c r="AN70">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AO70">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AP70">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AQ70">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AR70">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AS70">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="AT70">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15634,25 +15634,25 @@
         <v>1.63</v>
       </c>
       <c r="AN71">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AO71">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AP71">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR71">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="AS71">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AT71">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="AU71">
         <v>8</v>
@@ -15840,25 +15840,25 @@
         <v>1.21</v>
       </c>
       <c r="AN72">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO72">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AP72">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AQ72">
-        <v>0.89</v>
+        <v>1.47</v>
       </c>
       <c r="AR72">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AS72">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AT72">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="AU72">
         <v>5</v>
@@ -16049,22 +16049,22 @@
         <v>1</v>
       </c>
       <c r="AO73">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AP73">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AQ73">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AR73">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AS73">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AT73">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16252,25 +16252,25 @@
         <v>3.15</v>
       </c>
       <c r="AN74">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AO74">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AP74">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AQ74">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR74">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AS74">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AT74">
-        <v>2.69</v>
+        <v>3.01</v>
       </c>
       <c r="AU74">
         <v>14</v>
@@ -16458,25 +16458,25 @@
         <v>1.8</v>
       </c>
       <c r="AN75">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO75">
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AQ75">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AR75">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AS75">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="AT75">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16667,22 +16667,22 @@
         <v>0.6</v>
       </c>
       <c r="AO76">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AQ76">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR76">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AS76">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AT76">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AU76">
         <v>7</v>
@@ -16873,22 +16873,22 @@
         <v>1.6</v>
       </c>
       <c r="AO77">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP77">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AQ77">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="AR77">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AS77">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="AT77">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="AU77">
         <v>6</v>
@@ -17076,25 +17076,25 @@
         <v>1.44</v>
       </c>
       <c r="AN78">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO78">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AP78">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AQ78">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR78">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AS78">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AT78">
-        <v>3.49</v>
+        <v>3.43</v>
       </c>
       <c r="AU78">
         <v>4</v>
@@ -17282,25 +17282,25 @@
         <v>1.58</v>
       </c>
       <c r="AN79">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AO79">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AP79">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR79">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AS79">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AT79">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="AU79">
         <v>8</v>
@@ -17488,25 +17488,25 @@
         <v>1.41</v>
       </c>
       <c r="AN80">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AO80">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AP80">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AQ80">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR80">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="AS80">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AT80">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AU80">
         <v>4</v>
@@ -17694,25 +17694,25 @@
         <v>2.41</v>
       </c>
       <c r="AN81">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AO81">
-        <v>1.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR81">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AS81">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AT81">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -17900,25 +17900,25 @@
         <v>1.14</v>
       </c>
       <c r="AN82">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AO82">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AP82">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AQ82">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR82">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AS82">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AT82">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AU82">
         <v>3</v>
@@ -18106,25 +18106,25 @@
         <v>1.13</v>
       </c>
       <c r="AN83">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AO83">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="AP83">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AQ83">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AR83">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AS83">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AT83">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="AU83">
         <v>3</v>
@@ -18312,25 +18312,25 @@
         <v>1.6</v>
       </c>
       <c r="AN84">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AO84">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AP84">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AQ84">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AR84">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AS84">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AT84">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="AU84">
         <v>8</v>
@@ -18518,25 +18518,25 @@
         <v>1.93</v>
       </c>
       <c r="AN85">
-        <v>0.67</v>
+        <v>1.27</v>
       </c>
       <c r="AO85">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AP85">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="AQ85">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AR85">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AS85">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AT85">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18724,25 +18724,25 @@
         <v>1.71</v>
       </c>
       <c r="AN86">
-        <v>0.17</v>
+        <v>1.08</v>
       </c>
       <c r="AO86">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AP86">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AQ86">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="AR86">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AS86">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AT86">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -18930,25 +18930,25 @@
         <v>1.49</v>
       </c>
       <c r="AN87">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO87">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AQ87">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AR87">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AS87">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="AT87">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19136,25 +19136,25 @@
         <v>2.38</v>
       </c>
       <c r="AN88">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AO88">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AQ88">
-        <v>0.89</v>
+        <v>1.47</v>
       </c>
       <c r="AR88">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AS88">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AT88">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AU88">
         <v>10</v>
@@ -19342,25 +19342,25 @@
         <v>1.39</v>
       </c>
       <c r="AN89">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="AO89">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP89">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AQ89">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR89">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AS89">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="AT89">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19548,25 +19548,25 @@
         <v>1.08</v>
       </c>
       <c r="AN90">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO90">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP90">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AQ90">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR90">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AS90">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AT90">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AU90">
         <v>3</v>
@@ -19754,25 +19754,25 @@
         <v>3.2</v>
       </c>
       <c r="AN91">
-        <v>1.17</v>
+        <v>1.92</v>
       </c>
       <c r="AO91">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="AP91">
+        <v>1.79</v>
+      </c>
+      <c r="AQ91">
+        <v>0.79</v>
+      </c>
+      <c r="AR91">
+        <v>1.57</v>
+      </c>
+      <c r="AS91">
         <v>1.22</v>
       </c>
-      <c r="AQ91">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AR91">
-        <v>1.68</v>
-      </c>
-      <c r="AS91">
-        <v>0.95</v>
-      </c>
       <c r="AT91">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -19963,22 +19963,22 @@
         <v>1.83</v>
       </c>
       <c r="AO92">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AP92">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AQ92">
+        <v>1.16</v>
+      </c>
+      <c r="AR92">
         <v>1.56</v>
       </c>
-      <c r="AR92">
-        <v>1.7</v>
-      </c>
       <c r="AS92">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AT92">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20166,25 +20166,25 @@
         <v>5.6</v>
       </c>
       <c r="AN93">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AO93">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AP93">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AQ93">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR93">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AS93">
-        <v>0.96</v>
+        <v>1.19</v>
       </c>
       <c r="AT93">
-        <v>2.91</v>
+        <v>3.06</v>
       </c>
       <c r="AU93">
         <v>9</v>
@@ -20372,25 +20372,25 @@
         <v>1.95</v>
       </c>
       <c r="AN94">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="AO94">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AQ94">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AR94">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="AS94">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AT94">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AU94">
         <v>3</v>
@@ -20578,25 +20578,25 @@
         <v>1.1</v>
       </c>
       <c r="AN95">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AO95">
-        <v>2.67</v>
+        <v>1.85</v>
       </c>
       <c r="AP95">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AQ95">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AR95">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AS95">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AT95">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AU95">
         <v>4</v>
@@ -20784,25 +20784,25 @@
         <v>1.13</v>
       </c>
       <c r="AN96">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="AO96">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="AP96">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AQ96">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AR96">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AS96">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AT96">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -20990,25 +20990,25 @@
         <v>1.18</v>
       </c>
       <c r="AN97">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AO97">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AP97">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AQ97">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR97">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AS97">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AT97">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21196,25 +21196,25 @@
         <v>1.46</v>
       </c>
       <c r="AN98">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO98">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AP98">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AQ98">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AR98">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AS98">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="AT98">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AU98">
         <v>7</v>
@@ -21402,25 +21402,25 @@
         <v>1.58</v>
       </c>
       <c r="AN99">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AO99">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="AP99">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="AQ99">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AR99">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AS99">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AT99">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AU99">
         <v>7</v>
@@ -21608,25 +21608,25 @@
         <v>1.07</v>
       </c>
       <c r="AN100">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="AO100">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AP100">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AQ100">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AR100">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AS100">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AT100">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AU100">
         <v>2</v>
@@ -21814,25 +21814,25 @@
         <v>1.86</v>
       </c>
       <c r="AN101">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AO101">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AP101">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="AQ101">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR101">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AS101">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AT101">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="AU101">
         <v>4</v>
@@ -22020,25 +22020,25 @@
         <v>1.54</v>
       </c>
       <c r="AN102">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="AO102">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AP102">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AQ102">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR102">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="AS102">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AT102">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22226,25 +22226,25 @@
         <v>2.45</v>
       </c>
       <c r="AN103">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="AO103">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AP103">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AQ103">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR103">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AS103">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AT103">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22432,25 +22432,25 @@
         <v>1.12</v>
       </c>
       <c r="AN104">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AO104">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP104">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AQ104">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR104">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AS104">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AT104">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22638,25 +22638,25 @@
         <v>1.15</v>
       </c>
       <c r="AN105">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AO105">
-        <v>2.71</v>
+        <v>1.93</v>
       </c>
       <c r="AP105">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AQ105">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AR105">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AS105">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AT105">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="AU105">
         <v>3</v>
@@ -22844,25 +22844,25 @@
         <v>1.09</v>
       </c>
       <c r="AN106">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AO106">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AP106">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="AQ106">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR106">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AS106">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AT106">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="AU106">
         <v>2</v>
@@ -23050,25 +23050,25 @@
         <v>5.4</v>
       </c>
       <c r="AN107">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AO107">
-        <v>0.86</v>
+        <v>0.6</v>
       </c>
       <c r="AP107">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AQ107">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="AR107">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AS107">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="AT107">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23256,25 +23256,25 @@
         <v>1.6</v>
       </c>
       <c r="AN108">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO108">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AP108">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AQ108">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AR108">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AS108">
-        <v>0.89</v>
+        <v>1.07</v>
       </c>
       <c r="AT108">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23462,25 +23462,25 @@
         <v>4.1</v>
       </c>
       <c r="AN109">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AO109">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="AP109">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AQ109">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AR109">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AS109">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="AT109">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23668,25 +23668,25 @@
         <v>2.85</v>
       </c>
       <c r="AN110">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="AO110">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AP110">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AQ110">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AR110">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AS110">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AT110">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AU110">
         <v>6</v>
@@ -23874,25 +23874,25 @@
         <v>5</v>
       </c>
       <c r="AN111">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AO111">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AP111">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AQ111">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AR111">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AS111">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AT111">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="AU111">
         <v>7</v>
@@ -24080,25 +24080,25 @@
         <v>1.41</v>
       </c>
       <c r="AN112">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO112">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="AP112">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AQ112">
-        <v>0.89</v>
+        <v>1.47</v>
       </c>
       <c r="AR112">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AS112">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AT112">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AU112">
         <v>4</v>
@@ -24286,25 +24286,25 @@
         <v>1.75</v>
       </c>
       <c r="AN113">
-        <v>0.71</v>
+        <v>1.13</v>
       </c>
       <c r="AO113">
-        <v>1.71</v>
+        <v>1.13</v>
       </c>
       <c r="AP113">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AQ113">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR113">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AS113">
-        <v>0.87</v>
+        <v>1.1</v>
       </c>
       <c r="AT113">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AU113">
         <v>8</v>
@@ -24492,25 +24492,25 @@
         <v>1.59</v>
       </c>
       <c r="AN114">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO114">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP114">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="AQ114">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="AR114">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="AS114">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="AT114">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AU114">
         <v>5</v>
@@ -24701,22 +24701,22 @@
         <v>0.88</v>
       </c>
       <c r="AO115">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AP115">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR115">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AS115">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AT115">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24904,25 +24904,25 @@
         <v>2.2</v>
       </c>
       <c r="AN116">
-        <v>2.38</v>
+        <v>1.69</v>
       </c>
       <c r="AO116">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AQ116">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR116">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AS116">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AT116">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AU116">
         <v>3</v>
@@ -25110,25 +25110,25 @@
         <v>1.07</v>
       </c>
       <c r="AN117">
-        <v>0.63</v>
+        <v>1.06</v>
       </c>
       <c r="AO117">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AP117">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AQ117">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AR117">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="AS117">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AT117">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="AU117">
         <v>5</v>
@@ -25316,25 +25316,25 @@
         <v>1.75</v>
       </c>
       <c r="AN118">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AO118">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AP118">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="AQ118">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR118">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AS118">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AT118">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AU118">
         <v>2</v>
@@ -25522,25 +25522,25 @@
         <v>1.55</v>
       </c>
       <c r="AN119">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO119">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AP119">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AQ119">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AR119">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AS119">
         <v>1.65</v>
       </c>
       <c r="AT119">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AU119">
         <v>11</v>
@@ -25728,25 +25728,25 @@
         <v>1.09</v>
       </c>
       <c r="AN120">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AO120">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AP120">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AQ120">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR120">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AS120">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AT120">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -25934,25 +25934,25 @@
         <v>3.15</v>
       </c>
       <c r="AN121">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AO121">
-        <v>1</v>
+        <v>1.59</v>
       </c>
       <c r="AP121">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AQ121">
-        <v>0.89</v>
+        <v>1.47</v>
       </c>
       <c r="AR121">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AS121">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AT121">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26143,22 +26143,22 @@
         <v>1</v>
       </c>
       <c r="AO122">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AP122">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AQ122">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR122">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AS122">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AT122">
-        <v>2.79</v>
+        <v>2.98</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26346,25 +26346,25 @@
         <v>1.32</v>
       </c>
       <c r="AN123">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="AO123">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AP123">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AQ123">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AR123">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AS123">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AT123">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AU123">
         <v>3</v>
@@ -26552,25 +26552,25 @@
         <v>4.2</v>
       </c>
       <c r="AN124">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="AO124">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AQ124">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR124">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AS124">
-        <v>0.88</v>
+        <v>1.08</v>
       </c>
       <c r="AT124">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="AU124">
         <v>6</v>
@@ -26758,25 +26758,25 @@
         <v>5.2</v>
       </c>
       <c r="AN125">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AO125">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="AP125">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AQ125">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AR125">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AS125">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="AT125">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -26964,25 +26964,25 @@
         <v>1.74</v>
       </c>
       <c r="AN126">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AO126">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="AP126">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AQ126">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AR126">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AS126">
-        <v>0.92</v>
+        <v>1.05</v>
       </c>
       <c r="AT126">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AU126">
         <v>5</v>
@@ -27170,25 +27170,25 @@
         <v>1.75</v>
       </c>
       <c r="AN127">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="AO127">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AQ127">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AR127">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AS127">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AT127">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27376,25 +27376,25 @@
         <v>1.6</v>
       </c>
       <c r="AN128">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AO128">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="AP128">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="AQ128">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR128">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="AS128">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
       <c r="AT128">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AU128">
         <v>5</v>
@@ -27582,25 +27582,25 @@
         <v>1.12</v>
       </c>
       <c r="AN129">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO129">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AP129">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="AQ129">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR129">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AS129">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AT129">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="AU129">
         <v>2</v>
@@ -27788,25 +27788,25 @@
         <v>1.54</v>
       </c>
       <c r="AN130">
+        <v>1</v>
+      </c>
+      <c r="AO130">
+        <v>1.39</v>
+      </c>
+      <c r="AP130">
+        <v>0.95</v>
+      </c>
+      <c r="AQ130">
+        <v>1.47</v>
+      </c>
+      <c r="AR130">
         <v>1.11</v>
       </c>
-      <c r="AO130">
-        <v>1.33</v>
-      </c>
-      <c r="AP130">
-        <v>1</v>
-      </c>
-      <c r="AQ130">
-        <v>1.5</v>
-      </c>
-      <c r="AR130">
-        <v>1.17</v>
-      </c>
       <c r="AS130">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AT130">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="AU130">
         <v>5</v>
@@ -27994,25 +27994,25 @@
         <v>1.54</v>
       </c>
       <c r="AN131">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AO131">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AP131">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AQ131">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR131">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AS131">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AT131">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28200,25 +28200,25 @@
         <v>1.29</v>
       </c>
       <c r="AN132">
-        <v>2.11</v>
+        <v>1.5</v>
       </c>
       <c r="AO132">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="AP132">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AQ132">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AR132">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AS132">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AT132">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="AU132">
         <v>4</v>
@@ -28409,22 +28409,22 @@
         <v>2</v>
       </c>
       <c r="AO133">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="AP133">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AQ133">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AR133">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AS133">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AT133">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28615,22 +28615,22 @@
         <v>1</v>
       </c>
       <c r="AO134">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AQ134">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="AR134">
         <v>1.25</v>
       </c>
       <c r="AS134">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="AT134">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AU134">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="239">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1092,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP134"/>
+  <dimension ref="A1:BP135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1426,10 +1426,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AQ2">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1632,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1838,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2044,10 +2044,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AQ5">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
       <c r="AQ6">
-        <v>1.47</v>
+        <v>0.89</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2456,10 +2456,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AQ7">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2662,10 +2662,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AQ8">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2865,22 +2865,22 @@
         <v>0</v>
       </c>
       <c r="AO9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AQ9">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AR9">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AU9">
         <v>3</v>
@@ -3074,19 +3074,19 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ10">
-        <v>1.47</v>
+        <v>0.89</v>
       </c>
       <c r="AR10">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
         <v>4</v>
@@ -3280,10 +3280,10 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AQ11">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="AR11">
         <v>2.01</v>
@@ -3480,25 +3480,25 @@
         <v>1.7</v>
       </c>
       <c r="AN12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ12">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AR12">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3692,19 +3692,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AQ13">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AR13">
         <v>1.83</v>
       </c>
       <c r="AS13">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>3.09</v>
+        <v>1.83</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3895,22 +3895,22 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AQ14">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
       </c>
       <c r="AS14">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.59</v>
+        <v>1.21</v>
       </c>
       <c r="AU14">
         <v>6</v>
@@ -4098,25 +4098,25 @@
         <v>6.5</v>
       </c>
       <c r="AN15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AQ15">
-        <v>0.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR15">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS15">
         <v>0.36</v>
       </c>
       <c r="AT15">
-        <v>2.07</v>
+        <v>0.36</v>
       </c>
       <c r="AU15">
         <v>6</v>
@@ -4304,25 +4304,25 @@
         <v>1.05</v>
       </c>
       <c r="AN16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AQ16">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR16">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AT16">
-        <v>2.48</v>
+        <v>1.71</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4510,25 +4510,25 @@
         <v>2.2</v>
       </c>
       <c r="AN17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO17">
+        <v>3</v>
+      </c>
+      <c r="AP17">
+        <v>2</v>
+      </c>
+      <c r="AQ17">
         <v>1.5</v>
       </c>
-      <c r="AP17">
-        <v>1.47</v>
-      </c>
-      <c r="AQ17">
-        <v>1.47</v>
-      </c>
       <c r="AR17">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AT17">
-        <v>3.02</v>
+        <v>1.15</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4722,19 +4722,19 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR18">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AS18">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AT18">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="AU18">
         <v>8</v>
@@ -4922,25 +4922,25 @@
         <v>1.03</v>
       </c>
       <c r="AN19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AR19">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AS19">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT19">
-        <v>3.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU19">
         <v>2</v>
@@ -5128,25 +5128,25 @@
         <v>1.61</v>
       </c>
       <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0.5</v>
+      </c>
+      <c r="AQ20">
         <v>1.5</v>
       </c>
-      <c r="AO20">
-        <v>0.5</v>
-      </c>
-      <c r="AP20">
-        <v>1.05</v>
-      </c>
-      <c r="AQ20">
-        <v>1.26</v>
-      </c>
       <c r="AR20">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AS20">
-        <v>0.76</v>
+        <v>0.53</v>
       </c>
       <c r="AT20">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5337,22 +5337,22 @@
         <v>1</v>
       </c>
       <c r="AO21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
       <c r="AQ21">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AR21">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AS21">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>3.23</v>
+        <v>1.23</v>
       </c>
       <c r="AU21">
         <v>4</v>
@@ -5540,25 +5540,25 @@
         <v>1.05</v>
       </c>
       <c r="AN22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO22">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR22">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AT22">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AU22">
         <v>9</v>
@@ -5746,25 +5746,25 @@
         <v>1.63</v>
       </c>
       <c r="AN23">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO23">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AP23">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AQ23">
-        <v>0.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR23">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="AS23">
-        <v>1.11</v>
+        <v>0.6</v>
       </c>
       <c r="AT23">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -5952,25 +5952,25 @@
         <v>1.85</v>
       </c>
       <c r="AN24">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO24">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ24">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AR24">
-        <v>1.47</v>
+        <v>2.26</v>
       </c>
       <c r="AS24">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AT24">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6161,22 +6161,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ25">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AR25">
-        <v>1.23</v>
+        <v>0.98</v>
       </c>
       <c r="AS25">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AT25">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6367,22 +6367,22 @@
         <v>3</v>
       </c>
       <c r="AO26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AQ26">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AR26">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AS26">
-        <v>1.14</v>
+        <v>0.73</v>
       </c>
       <c r="AT26">
-        <v>2.78</v>
+        <v>2.21</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6573,22 +6573,22 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AQ27">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR27">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AS27">
-        <v>1.59</v>
+        <v>1.89</v>
       </c>
       <c r="AT27">
-        <v>3.26</v>
+        <v>3.84</v>
       </c>
       <c r="AU27">
         <v>4</v>
@@ -6776,25 +6776,25 @@
         <v>1.38</v>
       </c>
       <c r="AN28">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO28">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP28">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1.47</v>
+        <v>0.89</v>
       </c>
       <c r="AR28">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="AS28">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AT28">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="AU28">
         <v>7</v>
@@ -6982,25 +6982,25 @@
         <v>7.5</v>
       </c>
       <c r="AN29">
+        <v>2</v>
+      </c>
+      <c r="AO29">
+        <v>3</v>
+      </c>
+      <c r="AP29">
         <v>2.33</v>
       </c>
-      <c r="AO29">
-        <v>1</v>
-      </c>
-      <c r="AP29">
-        <v>1.95</v>
-      </c>
       <c r="AQ29">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AR29">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AS29">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="AT29">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7188,25 +7188,25 @@
         <v>1.06</v>
       </c>
       <c r="AN30">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AQ30">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AR30">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="AS30">
-        <v>1.56</v>
+        <v>1.09</v>
       </c>
       <c r="AT30">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AU30">
         <v>9</v>
@@ -7394,25 +7394,25 @@
         <v>1.14</v>
       </c>
       <c r="AN31">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO31">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR31">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS31">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AT31">
-        <v>3.32</v>
+        <v>3.01</v>
       </c>
       <c r="AU31">
         <v>5</v>
@@ -7600,25 +7600,25 @@
         <v>1.65</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP32">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AQ32">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AS32">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="AT32">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="AU32">
         <v>4</v>
@@ -7809,22 +7809,22 @@
         <v>0.5</v>
       </c>
       <c r="AO33">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AQ33">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AR33">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="AS33">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="AT33">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AU33">
         <v>5</v>
@@ -8012,25 +8012,25 @@
         <v>4.75</v>
       </c>
       <c r="AN34">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AO34">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AQ34">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR34">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AS34">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AT34">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AU34">
         <v>12</v>
@@ -8218,25 +8218,25 @@
         <v>2.05</v>
       </c>
       <c r="AN35">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AO35">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AP35">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
       <c r="AQ35">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="AR35">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AS35">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="AT35">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8424,25 +8424,25 @@
         <v>1.06</v>
       </c>
       <c r="AN36">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO36">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP36">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AR36">
-        <v>1.16</v>
+        <v>2.14</v>
       </c>
       <c r="AS36">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AT36">
-        <v>3.03</v>
+        <v>3.64</v>
       </c>
       <c r="AU36">
         <v>3</v>
@@ -8630,25 +8630,25 @@
         <v>1.64</v>
       </c>
       <c r="AN37">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AO37">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP37">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AQ37">
-        <v>0.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR37">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AS37">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="AT37">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AU37">
         <v>8</v>
@@ -8836,25 +8836,25 @@
         <v>1.96</v>
       </c>
       <c r="AN38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO38">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ38">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AR38">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="AS38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AT38">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="AU38">
         <v>3</v>
@@ -9042,25 +9042,25 @@
         <v>1.87</v>
       </c>
       <c r="AN39">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AO39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AQ39">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AR39">
-        <v>0.87</v>
+        <v>1.2</v>
       </c>
       <c r="AS39">
-        <v>1.07</v>
+        <v>0.68</v>
       </c>
       <c r="AT39">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9251,22 +9251,22 @@
         <v>2</v>
       </c>
       <c r="AO40">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AQ40">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AR40">
-        <v>1.79</v>
+        <v>2.09</v>
       </c>
       <c r="AS40">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AT40">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9454,25 +9454,25 @@
         <v>2.6</v>
       </c>
       <c r="AN41">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AO41">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41">
-        <v>1.47</v>
+        <v>0.89</v>
       </c>
       <c r="AR41">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AS41">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AT41">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="AU41">
         <v>4</v>
@@ -9660,25 +9660,25 @@
         <v>1.85</v>
       </c>
       <c r="AN42">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AO42">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AP42">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AQ42">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR42">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AS42">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AT42">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9866,25 +9866,25 @@
         <v>1.55</v>
       </c>
       <c r="AN43">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO43">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AQ43">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR43">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="AS43">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AT43">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="AU43">
         <v>3</v>
@@ -10075,22 +10075,22 @@
         <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
       <c r="AQ44">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AR44">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AS44">
-        <v>1.17</v>
+        <v>0.82</v>
       </c>
       <c r="AT44">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="AU44">
         <v>4</v>
@@ -10281,22 +10281,22 @@
         <v>1.33</v>
       </c>
       <c r="AO45">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AQ45">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AR45">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AS45">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AT45">
-        <v>2.87</v>
+        <v>2.99</v>
       </c>
       <c r="AU45">
         <v>6</v>
@@ -10484,25 +10484,25 @@
         <v>2.55</v>
       </c>
       <c r="AN46">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO46">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="AR46">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AS46">
-        <v>0.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT46">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="AU46">
         <v>5</v>
@@ -10690,25 +10690,25 @@
         <v>1.47</v>
       </c>
       <c r="AN47">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO47">
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ47">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AR47">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AS47">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
       <c r="AT47">
-        <v>2.21</v>
+        <v>1.72</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -10896,25 +10896,25 @@
         <v>1.39</v>
       </c>
       <c r="AN48">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AO48">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP48">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AQ48">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AR48">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="AS48">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="AT48">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="AU48">
         <v>2</v>
@@ -11105,22 +11105,22 @@
         <v>0.67</v>
       </c>
       <c r="AO49">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="AP49">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AQ49">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AR49">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AS49">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AT49">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AU49">
         <v>0</v>
@@ -11308,25 +11308,25 @@
         <v>1.49</v>
       </c>
       <c r="AN50">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO50">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AQ50">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR50">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AS50">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AT50">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11514,25 +11514,25 @@
         <v>1.6</v>
       </c>
       <c r="AN51">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AO51">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AP51">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AQ51">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR51">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AS51">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT51">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11720,25 +11720,25 @@
         <v>1.18</v>
       </c>
       <c r="AN52">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
       <c r="AQ52">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AR52">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS52">
-        <v>1.1</v>
+        <v>0.84</v>
       </c>
       <c r="AT52">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -11926,25 +11926,25 @@
         <v>1.3</v>
       </c>
       <c r="AN53">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AO53">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AQ53">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AR53">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AS53">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="AT53">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12132,25 +12132,25 @@
         <v>3.1</v>
       </c>
       <c r="AN54">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO54">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="AP54">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AQ54">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AR54">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AS54">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT54">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="AU54">
         <v>8</v>
@@ -12338,25 +12338,25 @@
         <v>1.16</v>
       </c>
       <c r="AN55">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AO55">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="AP55">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AQ55">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR55">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="AS55">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AT55">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12544,25 +12544,25 @@
         <v>2.14</v>
       </c>
       <c r="AN56">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO56">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP56">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
-        <v>0.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR56">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AS56">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="AT56">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="AU56">
         <v>11</v>
@@ -12750,25 +12750,25 @@
         <v>1.73</v>
       </c>
       <c r="AN57">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO57">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AQ57">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AR57">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AS57">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AT57">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="AU57">
         <v>0</v>
@@ -12959,22 +12959,22 @@
         <v>1.75</v>
       </c>
       <c r="AO58">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AQ58">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AR58">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AS58">
-        <v>1.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT58">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13162,25 +13162,25 @@
         <v>1.69</v>
       </c>
       <c r="AN59">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AO59">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP59">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AQ59">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="AR59">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="AS59">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="AT59">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AU59">
         <v>6</v>
@@ -13368,25 +13368,25 @@
         <v>1.08</v>
       </c>
       <c r="AN60">
-        <v>0.88</v>
+        <v>0.33</v>
       </c>
       <c r="AO60">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ60">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AR60">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AS60">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AT60">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13574,25 +13574,25 @@
         <v>1.08</v>
       </c>
       <c r="AN61">
-        <v>1.25</v>
+        <v>0.33</v>
       </c>
       <c r="AO61">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AP61">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ61">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR61">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="AS61">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AT61">
-        <v>3.09</v>
+        <v>3.31</v>
       </c>
       <c r="AU61">
         <v>4</v>
@@ -13780,25 +13780,25 @@
         <v>1.96</v>
       </c>
       <c r="AN62">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO62">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AP62">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AQ62">
-        <v>1.47</v>
+        <v>0.89</v>
       </c>
       <c r="AR62">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AS62">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT62">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -13986,25 +13986,25 @@
         <v>3.05</v>
       </c>
       <c r="AN63">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AO63">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AQ63">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="AS63">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT63">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14192,25 +14192,25 @@
         <v>1.41</v>
       </c>
       <c r="AN64">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AO64">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AQ64">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AR64">
-        <v>0.96</v>
+        <v>1.31</v>
       </c>
       <c r="AS64">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AT64">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="AU64">
         <v>4</v>
@@ -14398,25 +14398,25 @@
         <v>3.8</v>
       </c>
       <c r="AN65">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO65">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AP65">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AQ65">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR65">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AS65">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AT65">
-        <v>3.16</v>
+        <v>3.41</v>
       </c>
       <c r="AU65">
         <v>9</v>
@@ -14604,25 +14604,25 @@
         <v>1.48</v>
       </c>
       <c r="AN66">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AO66">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AP66">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AQ66">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AR66">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="AS66">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AT66">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14810,22 +14810,22 @@
         <v>2.2</v>
       </c>
       <c r="AN67">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO67">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AR67">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AS67">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="AT67">
         <v>2.33</v>
@@ -15016,25 +15016,25 @@
         <v>1.12</v>
       </c>
       <c r="AN68">
-        <v>1.11</v>
+        <v>0.2</v>
       </c>
       <c r="AO68">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AP68">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AQ68">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR68">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AS68">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AT68">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15222,25 +15222,25 @@
         <v>1.14</v>
       </c>
       <c r="AN69">
-        <v>1.22</v>
+        <v>0.8</v>
       </c>
       <c r="AO69">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
       <c r="AQ69">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AR69">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AS69">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AT69">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15428,25 +15428,25 @@
         <v>1.08</v>
       </c>
       <c r="AN70">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="AO70">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AQ70">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AR70">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AS70">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="AT70">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15634,25 +15634,25 @@
         <v>1.63</v>
       </c>
       <c r="AN71">
+        <v>1</v>
+      </c>
+      <c r="AO71">
+        <v>2</v>
+      </c>
+      <c r="AP71">
         <v>1.44</v>
       </c>
-      <c r="AO71">
-        <v>1.56</v>
-      </c>
-      <c r="AP71">
-        <v>1.47</v>
-      </c>
       <c r="AQ71">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AR71">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="AS71">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT71">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AU71">
         <v>8</v>
@@ -15840,25 +15840,25 @@
         <v>1.21</v>
       </c>
       <c r="AN72">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO72">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AQ72">
-        <v>1.47</v>
+        <v>0.89</v>
       </c>
       <c r="AR72">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AS72">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AT72">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="AU72">
         <v>5</v>
@@ -16049,22 +16049,22 @@
         <v>1</v>
       </c>
       <c r="AO73">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ73">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AR73">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AS73">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AT73">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16252,25 +16252,25 @@
         <v>3.15</v>
       </c>
       <c r="AN74">
+        <v>2.2</v>
+      </c>
+      <c r="AO74">
         <v>1.8</v>
       </c>
-      <c r="AO74">
-        <v>1.6</v>
-      </c>
       <c r="AP74">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AQ74">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AR74">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AS74">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AT74">
-        <v>3.01</v>
+        <v>2.69</v>
       </c>
       <c r="AU74">
         <v>14</v>
@@ -16458,25 +16458,25 @@
         <v>1.8</v>
       </c>
       <c r="AN75">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO75">
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AQ75">
-        <v>0.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR75">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AS75">
-        <v>1.06</v>
+        <v>0.75</v>
       </c>
       <c r="AT75">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16667,22 +16667,22 @@
         <v>0.6</v>
       </c>
       <c r="AO76">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AR76">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AS76">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AT76">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AU76">
         <v>7</v>
@@ -16873,22 +16873,22 @@
         <v>1.6</v>
       </c>
       <c r="AO77">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AP77">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AQ77">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="AR77">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AS77">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="AT77">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="AU77">
         <v>6</v>
@@ -17076,25 +17076,25 @@
         <v>1.44</v>
       </c>
       <c r="AN78">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO78">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AP78">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AQ78">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR78">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AS78">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AT78">
-        <v>3.43</v>
+        <v>3.49</v>
       </c>
       <c r="AU78">
         <v>4</v>
@@ -17282,25 +17282,25 @@
         <v>1.58</v>
       </c>
       <c r="AN79">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AO79">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AP79">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AQ79">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR79">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AS79">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AT79">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="AU79">
         <v>8</v>
@@ -17488,25 +17488,25 @@
         <v>1.41</v>
       </c>
       <c r="AN80">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="AO80">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AQ80">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AR80">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="AS80">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AT80">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AU80">
         <v>4</v>
@@ -17694,25 +17694,25 @@
         <v>2.41</v>
       </c>
       <c r="AN81">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AO81">
-        <v>0.91</v>
+        <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AR81">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AS81">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AT81">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -17900,25 +17900,25 @@
         <v>1.14</v>
       </c>
       <c r="AN82">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AO82">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AP82">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AQ82">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR82">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AS82">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AT82">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AU82">
         <v>3</v>
@@ -18106,25 +18106,25 @@
         <v>1.13</v>
       </c>
       <c r="AN83">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AO83">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="AP83">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ83">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AR83">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="AS83">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AT83">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AU83">
         <v>3</v>
@@ -18312,25 +18312,25 @@
         <v>1.6</v>
       </c>
       <c r="AN84">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AO84">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AQ84">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AR84">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AS84">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AT84">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="AU84">
         <v>8</v>
@@ -18518,25 +18518,25 @@
         <v>1.93</v>
       </c>
       <c r="AN85">
-        <v>1.27</v>
+        <v>0.67</v>
       </c>
       <c r="AO85">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="AP85">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
       <c r="AQ85">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AR85">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AS85">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AT85">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18724,25 +18724,25 @@
         <v>1.71</v>
       </c>
       <c r="AN86">
-        <v>1.08</v>
+        <v>0.17</v>
       </c>
       <c r="AO86">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AP86">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AQ86">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="AR86">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AS86">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AT86">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -18930,25 +18930,25 @@
         <v>1.49</v>
       </c>
       <c r="AN87">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO87">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP87">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AQ87">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AR87">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AS87">
-        <v>1.14</v>
+        <v>0.93</v>
       </c>
       <c r="AT87">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19136,25 +19136,25 @@
         <v>2.38</v>
       </c>
       <c r="AN88">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="AO88">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AQ88">
-        <v>1.47</v>
+        <v>0.89</v>
       </c>
       <c r="AR88">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AS88">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AT88">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="AU88">
         <v>10</v>
@@ -19342,25 +19342,25 @@
         <v>1.39</v>
       </c>
       <c r="AN89">
-        <v>1.08</v>
+        <v>0.8</v>
       </c>
       <c r="AO89">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ89">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AR89">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AS89">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="AT89">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19548,25 +19548,25 @@
         <v>1.08</v>
       </c>
       <c r="AN90">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO90">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP90">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AQ90">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR90">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AS90">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AT90">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="AU90">
         <v>3</v>
@@ -19754,25 +19754,25 @@
         <v>3.2</v>
       </c>
       <c r="AN91">
-        <v>1.92</v>
+        <v>1.17</v>
       </c>
       <c r="AO91">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AP91">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AQ91">
-        <v>0.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR91">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AS91">
-        <v>1.22</v>
+        <v>0.95</v>
       </c>
       <c r="AT91">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -19963,22 +19963,22 @@
         <v>1.83</v>
       </c>
       <c r="AO92">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AP92">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AQ92">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AR92">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AS92">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AT92">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20166,25 +20166,25 @@
         <v>5.6</v>
       </c>
       <c r="AN93">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AO93">
-        <v>1.08</v>
+        <v>2</v>
       </c>
       <c r="AP93">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AQ93">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AR93">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AS93">
-        <v>1.19</v>
+        <v>0.96</v>
       </c>
       <c r="AT93">
-        <v>3.06</v>
+        <v>2.91</v>
       </c>
       <c r="AU93">
         <v>9</v>
@@ -20372,25 +20372,25 @@
         <v>1.95</v>
       </c>
       <c r="AN94">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AO94">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP94">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AR94">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AS94">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AT94">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AU94">
         <v>3</v>
@@ -20578,25 +20578,25 @@
         <v>1.1</v>
       </c>
       <c r="AN95">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AO95">
-        <v>1.85</v>
+        <v>2.67</v>
       </c>
       <c r="AP95">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ95">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AR95">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AS95">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AT95">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="AU95">
         <v>4</v>
@@ -20784,25 +20784,25 @@
         <v>1.13</v>
       </c>
       <c r="AN96">
-        <v>1.23</v>
+        <v>0.83</v>
       </c>
       <c r="AO96">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="AP96">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AR96">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AS96">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AT96">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -20990,25 +20990,25 @@
         <v>1.18</v>
       </c>
       <c r="AN97">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AO97">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AP97">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ97">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR97">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AS97">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AT97">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21196,25 +21196,25 @@
         <v>1.46</v>
       </c>
       <c r="AN98">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AO98">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AQ98">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AR98">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AS98">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="AT98">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="AU98">
         <v>7</v>
@@ -21402,25 +21402,25 @@
         <v>1.58</v>
       </c>
       <c r="AN99">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="AO99">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AR99">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AS99">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AT99">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AU99">
         <v>7</v>
@@ -21608,25 +21608,25 @@
         <v>1.07</v>
       </c>
       <c r="AN100">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="AO100">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AP100">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AQ100">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AR100">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AS100">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AT100">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AU100">
         <v>2</v>
@@ -21814,25 +21814,25 @@
         <v>1.86</v>
       </c>
       <c r="AN101">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AO101">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AP101">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
       <c r="AQ101">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AR101">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AS101">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AT101">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="AU101">
         <v>4</v>
@@ -22020,25 +22020,25 @@
         <v>1.54</v>
       </c>
       <c r="AN102">
-        <v>1</v>
+        <v>0.29</v>
       </c>
       <c r="AO102">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AP102">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AQ102">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AR102">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="AS102">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AT102">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22226,25 +22226,25 @@
         <v>2.45</v>
       </c>
       <c r="AN103">
-        <v>1.71</v>
+        <v>2.29</v>
       </c>
       <c r="AO103">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AP103">
+        <v>2</v>
+      </c>
+      <c r="AQ103">
+        <v>1</v>
+      </c>
+      <c r="AR103">
         <v>1.47</v>
       </c>
-      <c r="AQ103">
-        <v>1.11</v>
-      </c>
-      <c r="AR103">
-        <v>1.28</v>
-      </c>
       <c r="AS103">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AT103">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22432,25 +22432,25 @@
         <v>1.12</v>
       </c>
       <c r="AN104">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AO104">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AP104">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AQ104">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR104">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AS104">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AT104">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22638,25 +22638,25 @@
         <v>1.15</v>
       </c>
       <c r="AN105">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AO105">
-        <v>1.93</v>
+        <v>2.71</v>
       </c>
       <c r="AP105">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AQ105">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AR105">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AS105">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AT105">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="AU105">
         <v>3</v>
@@ -22844,25 +22844,25 @@
         <v>1.09</v>
       </c>
       <c r="AN106">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="AO106">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AP106">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AQ106">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR106">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AS106">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AT106">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="AU106">
         <v>2</v>
@@ -23050,25 +23050,25 @@
         <v>5.4</v>
       </c>
       <c r="AN107">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AO107">
+        <v>0.86</v>
+      </c>
+      <c r="AP107">
+        <v>2.56</v>
+      </c>
+      <c r="AQ107">
         <v>0.6</v>
       </c>
-      <c r="AP107">
-        <v>2.26</v>
-      </c>
-      <c r="AQ107">
-        <v>0.47</v>
-      </c>
       <c r="AR107">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AS107">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="AT107">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23256,25 +23256,25 @@
         <v>1.6</v>
       </c>
       <c r="AN108">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AO108">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AP108">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ108">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AR108">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AS108">
-        <v>1.07</v>
+        <v>0.89</v>
       </c>
       <c r="AT108">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23462,25 +23462,25 @@
         <v>4.1</v>
       </c>
       <c r="AN109">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AO109">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="AP109">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AQ109">
-        <v>0.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR109">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AS109">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="AT109">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23668,25 +23668,25 @@
         <v>2.85</v>
       </c>
       <c r="AN110">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="AO110">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AP110">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AQ110">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AR110">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AS110">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AT110">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AU110">
         <v>6</v>
@@ -23874,25 +23874,25 @@
         <v>5</v>
       </c>
       <c r="AN111">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AO111">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="AP111">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AQ111">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AR111">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AS111">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AT111">
-        <v>2.91</v>
+        <v>2.99</v>
       </c>
       <c r="AU111">
         <v>7</v>
@@ -24080,25 +24080,25 @@
         <v>1.41</v>
       </c>
       <c r="AN112">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AO112">
-        <v>1.8</v>
+        <v>1.14</v>
       </c>
       <c r="AP112">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ112">
-        <v>1.47</v>
+        <v>0.89</v>
       </c>
       <c r="AR112">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AS112">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AT112">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="AU112">
         <v>4</v>
@@ -24286,25 +24286,25 @@
         <v>1.75</v>
       </c>
       <c r="AN113">
+        <v>0.71</v>
+      </c>
+      <c r="AO113">
+        <v>1.71</v>
+      </c>
+      <c r="AP113">
+        <v>1</v>
+      </c>
+      <c r="AQ113">
+        <v>1.5</v>
+      </c>
+      <c r="AR113">
         <v>1.13</v>
       </c>
-      <c r="AO113">
-        <v>1.13</v>
-      </c>
-      <c r="AP113">
-        <v>1.26</v>
-      </c>
-      <c r="AQ113">
-        <v>1.05</v>
-      </c>
-      <c r="AR113">
-        <v>1.07</v>
-      </c>
       <c r="AS113">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="AT113">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AU113">
         <v>8</v>
@@ -24492,25 +24492,25 @@
         <v>1.59</v>
       </c>
       <c r="AN114">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AO114">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="AP114">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AQ114">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="AR114">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="AS114">
-        <v>1.01</v>
+        <v>0.93</v>
       </c>
       <c r="AT114">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AU114">
         <v>5</v>
@@ -24701,22 +24701,22 @@
         <v>0.88</v>
       </c>
       <c r="AO115">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AP115">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AQ115">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR115">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AS115">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AT115">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24904,25 +24904,25 @@
         <v>2.2</v>
       </c>
       <c r="AN116">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="AO116">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AP116">
+        <v>2</v>
+      </c>
+      <c r="AQ116">
+        <v>1.5</v>
+      </c>
+      <c r="AR116">
         <v>1.47</v>
       </c>
-      <c r="AQ116">
-        <v>1.26</v>
-      </c>
-      <c r="AR116">
-        <v>1.28</v>
-      </c>
       <c r="AS116">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AT116">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="AU116">
         <v>3</v>
@@ -25110,25 +25110,25 @@
         <v>1.07</v>
       </c>
       <c r="AN117">
-        <v>1.06</v>
+        <v>0.63</v>
       </c>
       <c r="AO117">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="AP117">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AQ117">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AR117">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="AS117">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AT117">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="AU117">
         <v>5</v>
@@ -25316,25 +25316,25 @@
         <v>1.75</v>
       </c>
       <c r="AN118">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AO118">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AP118">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
       <c r="AQ118">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AR118">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AS118">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AT118">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AU118">
         <v>2</v>
@@ -25522,25 +25522,25 @@
         <v>1.55</v>
       </c>
       <c r="AN119">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AO119">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AP119">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AQ119">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AR119">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AS119">
         <v>1.65</v>
       </c>
       <c r="AT119">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AU119">
         <v>11</v>
@@ -25728,25 +25728,25 @@
         <v>1.09</v>
       </c>
       <c r="AN120">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AO120">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AP120">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AQ120">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR120">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AS120">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AT120">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -25934,25 +25934,25 @@
         <v>3.15</v>
       </c>
       <c r="AN121">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AO121">
-        <v>1.59</v>
+        <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AQ121">
-        <v>1.47</v>
+        <v>0.89</v>
       </c>
       <c r="AR121">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AS121">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AT121">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26143,22 +26143,22 @@
         <v>1</v>
       </c>
       <c r="AO122">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AP122">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ122">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR122">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AS122">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AT122">
-        <v>2.98</v>
+        <v>2.79</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26346,25 +26346,25 @@
         <v>1.32</v>
       </c>
       <c r="AN123">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="AO123">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AP123">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AQ123">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AR123">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AS123">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AT123">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AU123">
         <v>3</v>
@@ -26552,25 +26552,25 @@
         <v>4.2</v>
       </c>
       <c r="AN124">
-        <v>1.94</v>
+        <v>1.38</v>
       </c>
       <c r="AO124">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AQ124">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AR124">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AS124">
-        <v>1.08</v>
+        <v>0.88</v>
       </c>
       <c r="AT124">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AU124">
         <v>6</v>
@@ -26758,25 +26758,25 @@
         <v>5.2</v>
       </c>
       <c r="AN125">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AO125">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AP125">
+        <v>2.33</v>
+      </c>
+      <c r="AQ125">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR125">
         <v>1.95</v>
       </c>
-      <c r="AQ125">
-        <v>0.79</v>
-      </c>
-      <c r="AR125">
-        <v>1.85</v>
-      </c>
       <c r="AS125">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="AT125">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -26964,25 +26964,25 @@
         <v>1.74</v>
       </c>
       <c r="AN126">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AO126">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="AP126">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ126">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AR126">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AS126">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="AT126">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AU126">
         <v>5</v>
@@ -27170,25 +27170,25 @@
         <v>1.75</v>
       </c>
       <c r="AN127">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AO127">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP127">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AR127">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AS127">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AT127">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27376,25 +27376,25 @@
         <v>1.6</v>
       </c>
       <c r="AN128">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AO128">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AQ128">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AR128">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AS128">
-        <v>1.09</v>
+        <v>0.93</v>
       </c>
       <c r="AT128">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AU128">
         <v>5</v>
@@ -27582,25 +27582,25 @@
         <v>1.12</v>
       </c>
       <c r="AN129">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AO129">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="AP129">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
       <c r="AQ129">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR129">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AS129">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AT129">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="AU129">
         <v>2</v>
@@ -27788,25 +27788,25 @@
         <v>1.54</v>
       </c>
       <c r="AN130">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AO130">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AP130">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AQ130">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AR130">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AS130">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AT130">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="AU130">
         <v>5</v>
@@ -27994,25 +27994,25 @@
         <v>1.54</v>
       </c>
       <c r="AN131">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AO131">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AQ131">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AR131">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AS131">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AT131">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28200,25 +28200,25 @@
         <v>1.29</v>
       </c>
       <c r="AN132">
-        <v>1.5</v>
+        <v>2.11</v>
       </c>
       <c r="AO132">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="AP132">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AQ132">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AR132">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AS132">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AT132">
-        <v>2.86</v>
+        <v>2.97</v>
       </c>
       <c r="AU132">
         <v>4</v>
@@ -28409,22 +28409,22 @@
         <v>2</v>
       </c>
       <c r="AO133">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="AP133">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AQ133">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AR133">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AS133">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AT133">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28615,22 +28615,22 @@
         <v>1</v>
       </c>
       <c r="AO134">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP134">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ134">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="AR134">
         <v>1.25</v>
       </c>
       <c r="AS134">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="AT134">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="AU134">
         <v>7</v>
@@ -28697,6 +28697,212 @@
       </c>
       <c r="BP134">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7537426</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45681.625</v>
+      </c>
+      <c r="F135">
+        <v>20</v>
+      </c>
+      <c r="G135" t="s">
+        <v>70</v>
+      </c>
+      <c r="H135" t="s">
+        <v>74</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+      <c r="N135">
+        <v>1</v>
+      </c>
+      <c r="O135" t="s">
+        <v>84</v>
+      </c>
+      <c r="P135" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q135">
+        <v>3.75</v>
+      </c>
+      <c r="R135">
+        <v>1.91</v>
+      </c>
+      <c r="S135">
+        <v>3.4</v>
+      </c>
+      <c r="T135">
+        <v>1.57</v>
+      </c>
+      <c r="U135">
+        <v>2.25</v>
+      </c>
+      <c r="V135">
+        <v>3.75</v>
+      </c>
+      <c r="W135">
+        <v>1.25</v>
+      </c>
+      <c r="X135">
+        <v>13</v>
+      </c>
+      <c r="Y135">
+        <v>1.04</v>
+      </c>
+      <c r="Z135">
+        <v>3.04</v>
+      </c>
+      <c r="AA135">
+        <v>3.02</v>
+      </c>
+      <c r="AB135">
+        <v>2.55</v>
+      </c>
+      <c r="AC135">
+        <v>1.1</v>
+      </c>
+      <c r="AD135">
+        <v>4.4</v>
+      </c>
+      <c r="AE135">
+        <v>1.5</v>
+      </c>
+      <c r="AF135">
+        <v>2.44</v>
+      </c>
+      <c r="AG135">
+        <v>2.4</v>
+      </c>
+      <c r="AH135">
+        <v>1.5</v>
+      </c>
+      <c r="AI135">
+        <v>2.1</v>
+      </c>
+      <c r="AJ135">
+        <v>1.67</v>
+      </c>
+      <c r="AK135">
+        <v>1.52</v>
+      </c>
+      <c r="AL135">
+        <v>1.39</v>
+      </c>
+      <c r="AM135">
+        <v>1.4</v>
+      </c>
+      <c r="AN135">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AO135">
+        <v>1.56</v>
+      </c>
+      <c r="AP135">
+        <v>0.5</v>
+      </c>
+      <c r="AQ135">
+        <v>1.7</v>
+      </c>
+      <c r="AR135">
+        <v>1.26</v>
+      </c>
+      <c r="AS135">
+        <v>1.06</v>
+      </c>
+      <c r="AT135">
+        <v>2.32</v>
+      </c>
+      <c r="AU135">
+        <v>3</v>
+      </c>
+      <c r="AV135">
+        <v>3</v>
+      </c>
+      <c r="AW135">
+        <v>7</v>
+      </c>
+      <c r="AX135">
+        <v>4</v>
+      </c>
+      <c r="AY135">
+        <v>11</v>
+      </c>
+      <c r="AZ135">
+        <v>7</v>
+      </c>
+      <c r="BA135">
+        <v>4</v>
+      </c>
+      <c r="BB135">
+        <v>2</v>
+      </c>
+      <c r="BC135">
+        <v>6</v>
+      </c>
+      <c r="BD135">
+        <v>2.18</v>
+      </c>
+      <c r="BE135">
+        <v>6.1</v>
+      </c>
+      <c r="BF135">
+        <v>1.84</v>
+      </c>
+      <c r="BG135">
+        <v>1.5</v>
+      </c>
+      <c r="BH135">
+        <v>2.23</v>
+      </c>
+      <c r="BI135">
+        <v>1.84</v>
+      </c>
+      <c r="BJ135">
+        <v>1.76</v>
+      </c>
+      <c r="BK135">
+        <v>2.35</v>
+      </c>
+      <c r="BL135">
+        <v>1.46</v>
+      </c>
+      <c r="BM135">
+        <v>3.2</v>
+      </c>
+      <c r="BN135">
+        <v>1.26</v>
+      </c>
+      <c r="BO135">
+        <v>4.3</v>
+      </c>
+      <c r="BP135">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
